--- a/docs/xlsx/jobs-2026-10-29.xlsx
+++ b/docs/xlsx/jobs-2026-10-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="636">
   <si>
     <t>Title</t>
   </si>
@@ -40,18 +40,1269 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Assistant Division Chief, Technical Analysis Section (Environmental Manager II)</t>
+  </si>
+  <si>
+    <t>Maryland State Highway Administration</t>
+  </si>
+  <si>
+    <t>Baltimore, MD</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$93,138 - $146,883 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-division-chief-technical-analysis-section-environmental-manager-ii-baltimore-maryland/7009244263</t>
+  </si>
+  <si>
+    <t>Attorney III</t>
+  </si>
+  <si>
+    <t>Office of Energy Infrastructure Safety</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$10,852 - $15,325 per month</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-attorney-iii-sacramento-california/6653979891</t>
+  </si>
+  <si>
+    <t>Biosecurity Coordinator-5 - Guam</t>
+  </si>
+  <si>
+    <t>CEMML</t>
+  </si>
+  <si>
+    <t>Santa Rita, Guam, Other</t>
+  </si>
+  <si>
+    <t>$70,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biosecurity-coordinator-5---guam-santa-rita-guam-other/9554478417</t>
+  </si>
+  <si>
+    <t>Botany Subject Matter Expert</t>
+  </si>
+  <si>
+    <t>Leesville, LA</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botany-subject-matter-expert-leesville-louisiana/7379465454</t>
+  </si>
+  <si>
+    <t>California Condor Monitoring Technician (Yurok Tribe, Orick, CA)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Orick, CA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>Living Allowance: $510.66 biweekly. Education Award: $5176.50.</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-california-condor-monitoring-technician-yurok-tribe-orick-ca-orick-california/3288748468</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay Program's Clean Water Goal Team Staffer</t>
+  </si>
+  <si>
+    <t>Chesapeake Research Consortium</t>
+  </si>
+  <si>
+    <t>Annapolis, MD</t>
+  </si>
+  <si>
+    <t>$52,432 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chesapeake-bay-programs-clean-water-goal-team-staffer-annapolis-maryland/9760150627</t>
+  </si>
+  <si>
+    <t>Coastal Naturalist</t>
+  </si>
+  <si>
+    <t>Camp Ocean Pines</t>
+  </si>
+  <si>
+    <t>Cambria, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19 - $21 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coastal-naturalist-cambria-california/5703637346</t>
+  </si>
+  <si>
+    <t>Conservation Planner</t>
+  </si>
+  <si>
+    <t>Trinity County Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Weaverville, CA</t>
+  </si>
+  <si>
+    <t>$28 - $30.87 per hour</t>
+  </si>
+  <si>
+    <t>forestry-hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-planner-weaverville-california/4306311014</t>
+  </si>
+  <si>
+    <t>East Coast Organizer</t>
+  </si>
+  <si>
+    <t>Southern Utah Wilderness Alliance</t>
+  </si>
+  <si>
+    <t>Salt Lake City, UT</t>
+  </si>
+  <si>
+    <t>$72,000 - $77,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-east-coast-organizer-salt-lake-city-utah/3815457807</t>
+  </si>
+  <si>
+    <t>Education and Visitor Services Technician (BLM, Carrizo Plains National Monument)</t>
+  </si>
+  <si>
+    <t>Bakersfield, CA</t>
+  </si>
+  <si>
+    <t>Living Allowance: $1400 biweekly. Education Award: $1956.35.</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-and-visitor-services-technician-blm-carrizo-plains-national-monument-bakersfield-california/9503889012</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Trainer and Technical Assistance Provider (Part-time)</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Lowell, MA</t>
+  </si>
+  <si>
+    <t>$50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-analyst--trainer-and-technical-assistance-provider-part-time-lowell-massachusetts/2800181526</t>
+  </si>
+  <si>
+    <t>Environmental Education AmeriCorps Member</t>
+  </si>
+  <si>
+    <t>Audubon Vermont</t>
+  </si>
+  <si>
+    <t>Huntington, VT</t>
+  </si>
+  <si>
+    <t>$31,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-americorps-member-huntington-vermont/9765696912</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Lake Waramaug Conservancy</t>
+  </si>
+  <si>
+    <t>Warren, CT</t>
+  </si>
+  <si>
+    <t>$110,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-ecology-hydrology-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-warren-connecticut/9893338614</t>
+  </si>
+  <si>
+    <t>Facility Manager</t>
+  </si>
+  <si>
+    <t>Deer Hill Expeditions</t>
+  </si>
+  <si>
+    <t>Mancos, CO</t>
+  </si>
+  <si>
+    <t>$52,000 - $58,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facility-manager-mancos-colorado/6329755637</t>
+  </si>
+  <si>
+    <t>Field Investigator (Analyst III)</t>
+  </si>
+  <si>
+    <t>Sacramento, Oakland, or Lakewood, CA</t>
+  </si>
+  <si>
+    <t>$6,623 - $8,290 per month</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-investigator-analyst-iii-sacramento-oakland-or-lakewood-california/2265210691</t>
+  </si>
+  <si>
+    <t>Fisheries Technician 1- Tagging Trailer Assistant</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Red Bluff, CA</t>
+  </si>
+  <si>
+    <t>$15.59 - $25.46 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-1--tagging-trailer-assistant-red-bluff-california/6674608841</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 1- Tagging Trailer Operator</t>
+  </si>
+  <si>
+    <t>$19.58 - $31.54 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-1--tagging-trailer-operator-red-bluff-california/8747868213</t>
+  </si>
+  <si>
+    <t>Fishing Line Recycling Program Intern</t>
+  </si>
+  <si>
+    <t>Point Blue Conservation Science</t>
+  </si>
+  <si>
+    <t>Lompoc, CA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$19.70 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishing-line-recycling-program-intern-lompoc-california/7854004805</t>
+  </si>
+  <si>
+    <t>Fixed-Wing Instructor Pilot</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Tumwater, WA</t>
+  </si>
+  <si>
+    <t>$7,044 - $9,478 per month</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fixed-wing-instructor-pilot-tumwater-washington/8847705414</t>
+  </si>
+  <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever Inc, and Quail Forever</t>
+  </si>
+  <si>
+    <t>St Paul, MN</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-human-resources-generalist-st-paul-minnesota/9570216223</t>
+  </si>
+  <si>
+    <t>Land Stewardship Specialist</t>
+  </si>
+  <si>
+    <t>Tar River Land Conservancy</t>
+  </si>
+  <si>
+    <t>Louisburg, NC</t>
+  </si>
+  <si>
+    <t>$48,000 - $57,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-stewardship-specialist-louisburg-north-carolina/2797232916</t>
+  </si>
+  <si>
+    <t>NC Sandhills Stewardship Manager</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>Southern Pines, NC</t>
+  </si>
+  <si>
+    <t>$66,000 - $78,000 per year</t>
+  </si>
+  <si>
+    <t>forestry-restoration-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nc-sandhills-stewardship-manager-southern-pines-north-carolina/3525482642</t>
+  </si>
+  <si>
+    <t>Paid Marine Science Education Internship</t>
+  </si>
+  <si>
+    <t>The Pigeon Key Foundation</t>
+  </si>
+  <si>
+    <t>Marathon, FL</t>
+  </si>
+  <si>
+    <t>$1,000 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paid-marine-science-education-internship-marathon-florida/3190202875</t>
+  </si>
+  <si>
+    <t>Research Coordinator of Anthropology</t>
+  </si>
+  <si>
+    <t>University of Oklahoma</t>
+  </si>
+  <si>
+    <t>Norman, OK</t>
+  </si>
+  <si>
+    <t>$48,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-coordinator-of-anthropology-norman-oklahoma/7069740059</t>
+  </si>
+  <si>
+    <t>Senior Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>Denver Zoo Conservation Alliance</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>$138,000 - $172,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-director-of-philanthropy-denver-colorado/6257298143</t>
+  </si>
+  <si>
+    <t>Small Utility Project I</t>
+  </si>
+  <si>
+    <t>Rural Community Assistance Corporation</t>
+  </si>
+  <si>
+    <t>West Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$76,103 - $83,976 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-small-utility-project-i-west-sacramento-california/2321907968</t>
+  </si>
+  <si>
+    <t>Software Engineer (Python / Django)</t>
+  </si>
+  <si>
+    <t>Felidae Conservation Fund</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>volunteer</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-software-engineer-python--django-remote-remote/2170982833</t>
+  </si>
+  <si>
+    <t>Spring Outdoor Education Logistics Intern</t>
+  </si>
+  <si>
+    <t>$1,584 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-education-logistics-intern-spring-mancos-colorado/8357379358</t>
+  </si>
+  <si>
+    <t>Summer Camp Staff</t>
+  </si>
+  <si>
+    <t>Camp Fire Minneosta</t>
+  </si>
+  <si>
+    <t>Excelsior, MN</t>
+  </si>
+  <si>
+    <t>$620 - $700 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-camp-staff-excelsior-minnesota/5551180572</t>
+  </si>
+  <si>
+    <t>Summer Outdoor Education Logistics Intern</t>
+  </si>
+  <si>
+    <t>$1,540 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-outdoor-education-logistics-intern-mancos-colorado/5487991739</t>
+  </si>
+  <si>
+    <t>TPWD - Park/Historic Site Superintendent I</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Rocksprings, TX</t>
+  </si>
+  <si>
+    <t>$5,912.72 - $6,912.72 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---parkhistoric-site-superintendent-i-rocksprings-texas/6477706354</t>
+  </si>
+  <si>
+    <t>Trails Data Specialist - Sedona, AZ</t>
+  </si>
+  <si>
+    <t>Arizona Conservation Corps</t>
+  </si>
+  <si>
+    <t>Sedona, AZ</t>
+  </si>
+  <si>
+    <t>$775 per week</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trails-data-specialist---sedona-az-sedona-arizona/7013108025</t>
+  </si>
+  <si>
+    <t>TWDB - 27-21 Environmental Protection Specialist I-III</t>
+  </si>
+  <si>
+    <t>Texas Water Development Board</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$3,409.84 - $5,381.25 per month</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---27-21-environmental-protection-specialist-i-iii-austin-texas/6574537596</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>$165,000 - $185,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-of-programs-denver-colorado/2393106332</t>
+  </si>
+  <si>
+    <t>Virginia Field Coordinator</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Wilderness Stewards</t>
+  </si>
+  <si>
+    <t>Roanoke, VA</t>
+  </si>
+  <si>
+    <t>$26 - $27 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-virginia-field-coordinator-roanoke-virginia/6576872093</t>
+  </si>
+  <si>
+    <t>Wetland Restoration Ecologist</t>
+  </si>
+  <si>
+    <t>California Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Stockton, CA</t>
+  </si>
+  <si>
+    <t>$8,055 - $11,054 per month</t>
+  </si>
+  <si>
+    <t>ecology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-restoration-ecologist-stockton-california/3671165513</t>
+  </si>
+  <si>
+    <t>Wildlife Conflict Mitigation Biologist</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Panama City, FL</t>
+  </si>
+  <si>
+    <t>$23.44 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-conflict-mitigation-biologist-panama-city-florida/6572804249</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>SCELP</t>
+  </si>
+  <si>
+    <t>Greenville, South Carolina, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/staff-attorney-8/</t>
+  </si>
+  <si>
+    <t>Accountant (remote)</t>
+  </si>
+  <si>
+    <t>Fohrman &amp; Fohrman, Inc.</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/71173879db8346de998379c9278d59a4-accountant-remote-fohrman-fohrman-inc-dana-point</t>
+  </si>
+  <si>
+    <t>Administrative Assistant, Immigration Practice</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c24e79e53434f7ebd372ec0e550f5dd-administrative-assistant-immigration-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Algebra I and II Instructors- After School - Liberty LEADS</t>
+  </si>
+  <si>
+    <t>Liberty LEADS in New York City</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/287ada512aff4c968bfd0aceff1c46d3-algebra-i-and-ii-instructors-after-school-liberty-leads-liberty-leads-in-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Director - Urban Institute of Mathematics</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 24.73 - 24.73/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/539c130d02e84cc9935a7c4f9f49b43d-assistant-director-urban-institute-of-mathematics-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>ASSOC VICE CHANCELLOR-FINANCE &amp; OPERATIONS (CCC FOUNDATION)</t>
+  </si>
+  <si>
+    <t>City Colleges Of Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7a5fd10595a45d3b24ea3965a71364a-assoc-vice-chancellor-finance-operations-ccc-foundation-city-colleges-of-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Associate Director of Development, Individual &amp; Corporate Giving</t>
+  </si>
+  <si>
+    <t>C&amp;O Canal Trust</t>
+  </si>
+  <si>
+    <t>Williamsport, Maryland</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1900714edb3e494689d65ca56c0be42d-associate-director-of-development-individual-corporate-giving-co-canal-trust-williamsport</t>
+  </si>
+  <si>
+    <t>Associate Director of Real Estate</t>
+  </si>
+  <si>
+    <t>PSwrx</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Financial Literacy Personal Finance, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b4fc5d7e561483b905431bcae70c659-associate-director-of-real-estate-pswrx-new-york</t>
+  </si>
+  <si>
+    <t>Budget Analyst</t>
+  </si>
+  <si>
+    <t>NYC Campaign Finance Board</t>
+  </si>
+  <si>
+    <t>USD 80001.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ecb6e88ea7ae4f25b12c20986b4ccc39-budget-analyst-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
+    <t>Business / Development Manager</t>
+  </si>
+  <si>
+    <t>THE GOOD DOG FOUNDATION</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/299dbcf9aae143408b248f76dedf98e6-business-development-manager-the-good-dog-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Chief of Partnerships</t>
+  </si>
+  <si>
+    <t>World Justice Project</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 136500.00 - 230000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f0c77cde6c44e63a5a9547cf0e95d16-chief-of-partnerships-world-justice-project-washington</t>
+  </si>
+  <si>
+    <t>Client Services Coordinator</t>
+  </si>
+  <si>
+    <t>Office of the Appellate Defender</t>
+  </si>
+  <si>
+    <t>USD 62730.00 - 73604.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0ddfe886a744afaae485bc98c9d417d-client-services-coordinator-office-of-the-appellate-defender-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Outreach Associate</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Lgbtq, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/658d093080c440d186e49efea5de5f97-communications-and-outreach-associate-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Louisiana Bucket Brigade</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6e35db81aae4f6da82f5ce644990ed6-communications-manager-louisiana-bucket-brigade-new-orleans</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT MANAGER — BOSTON</t>
+  </si>
+  <si>
+    <t>Positive Tracks</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73500.00 - 73500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f309418436264dea95c1488224b768d7-community-engagement-manager-boston-positive-tracks-boston</t>
+  </si>
+  <si>
+    <t>Community Manager</t>
+  </si>
+  <si>
+    <t>Yoga Alliance</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c07a921c64e4d37bb37263851ab0974-community-manager-yoga-alliance-arlington</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Qsource</t>
+  </si>
+  <si>
+    <t>USD 105000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e28fe0bd6fc4c1cb950ed1beb632602-controller-qsource-memphis</t>
+  </si>
+  <si>
+    <t>Database and Development Lead</t>
+  </si>
+  <si>
+    <t>ALL STARS PROJECT INC.</t>
+  </si>
+  <si>
+    <t>Житомир, Zhytomyrska, UA</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/07da6819679e43e48d8036ab50408d86-database-and-development-lead-all-stars-project-inc-zhitomir</t>
+  </si>
+  <si>
+    <t>Development &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Friends of the Jerusalem Youth Chorus</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b0aa1a7333143728f6ba2ab9e072275-development-operations-coordinator-friends-of-the-jerusalem-youth-chorus-boston</t>
+  </si>
+  <si>
+    <t>Development Coordinator, Regional Office New York</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17ac1310c1594ed6bd80d3d7cc7b00a7-development-coordinator-regional-office-new-york-ajc-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Refugee Artisan Initiative</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edd9f1deb5b84d248e4c3f401a2ebbb1-development-director-refugee-artisan-initiative-seattle</t>
+  </si>
+  <si>
+    <t>Development Initiatives Coordinator Southeast</t>
+  </si>
+  <si>
+    <t>Shalom Hartman Institute of North America</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbb991a789b644b88154fac511f59118-development-initiatives-coordinator-southeast-shalom-hartman-institute-of-north-america-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications &amp; Knowledge Translation</t>
+  </si>
+  <si>
+    <t>Health Care Without Harm (HCWH) Europe</t>
+  </si>
+  <si>
+    <t>Remote (BE)</t>
+  </si>
+  <si>
+    <t>EUR 73000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e8c4a2bd07b441ea9f58e9c2ec67844-director-of-communications-knowledge-translation-health-care-without-harm-hcwh-europe-brussels</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Mothers Against Media Addiction (MAMA)</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Consumer Protection, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1aebf152e7444fcaf4ccea92a1127d8-director-of-development-mothers-against-media-addiction-mama-new-york</t>
+  </si>
+  <si>
+    <t>Director of Grassroots Advocacy</t>
+  </si>
+  <si>
+    <t>Advocates for Community Health, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5ee39fc9f0f4921bacea9305ee98a65-director-of-grassroots-advocacy-advocates-for-community-health-inc-washington</t>
+  </si>
+  <si>
+    <t>Director of Member Programs</t>
+  </si>
+  <si>
+    <t>Philadelphia Association of Community Development Corporations (PACDC)</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f6a31c8f539d4dccadbcbe9d06b39bfb-director-of-member-programs-philadelphia-association-of-community-development-corporations-pacdc-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of People &amp; Operations</t>
+  </si>
+  <si>
+    <t>Global Village Project</t>
+  </si>
+  <si>
+    <t>Decatur, Georgia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9746ebe487c94520a6a650d0d56083f0-director-of-people-operations-global-village-project-decatur</t>
+  </si>
+  <si>
+    <t>Director of Volunteer &amp; Community Engagement</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity of Washington DC &amp; Northern Virginia</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad82fdab632943ce8201e5103455bfdb-director-of-volunteer-community-engagement-habitat-for-humanity-of-washington-dc-northern-virginia-arlington</t>
+  </si>
+  <si>
+    <t>Director, AI Education Initiatives (ai4CCNY)</t>
+  </si>
+  <si>
+    <t>The Foundation for City College</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5aada413e804422ebdc01a506fb8da3d-director-ai-education-initiatives-ai4ccny-the-foundation-for-city-college-new-york</t>
+  </si>
+  <si>
+    <t>Editor, Moldova</t>
+  </si>
+  <si>
+    <t>Organized Crime and Corruption Reporting Project</t>
+  </si>
+  <si>
+    <t>Remote (MD)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49c5fc86bba344378ff5192b15133548-editor-moldova-organized-crime-and-corruption-reporting-project-amsterdam</t>
+  </si>
+  <si>
+    <t>Employment Attorney for Nonprofit/Tax-Exempt Organizations (part-time)</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/67800d49ceb9441ab6afc1f8bb274d2f-employment-attorney-for-nonprofittax-exempt-organizations-part-time-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Missouri Foundation for Health</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 67500.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27aebbf0d2b94e9f908383e34c8e4cd2-executive-assistant-missouri-foundation-for-health-st-louis</t>
+  </si>
+  <si>
+    <t>Executive Assistant &amp; Constituent Relations Associate</t>
+  </si>
+  <si>
+    <t>Counterterrorism Education Learning Lab (CELL)</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03f749c969e44de8bbea42151d5fbaf8-executive-assistant-constituent-relations-associate-counterterrorism-education-learning-lab-cell-denver</t>
+  </si>
+  <si>
+    <t>Tulsa County Medical Society</t>
+  </si>
+  <si>
+    <t>Tulsa, Oklahoma</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3eb89340da0494eb2339e5e3934cb40-executive-director-tulsa-county-medical-society-tulsa</t>
+  </si>
+  <si>
+    <t>Executive Director, Downtown Ashland Association</t>
+  </si>
+  <si>
+    <t>Town of Ashland, Virginia</t>
+  </si>
+  <si>
+    <t>Ashland, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1589e780f21e45deb9576a9c63fc2b8b-executive-director-downtown-ashland-association-town-of-ashland-virginia-ashland</t>
+  </si>
+  <si>
+    <t>Finance Associate</t>
+  </si>
+  <si>
+    <t>RF CUNY (Institute for Justice and Opportunity)</t>
+  </si>
+  <si>
+    <t>Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9fc501d88a0e4cecb2fa1f530fc176f7-finance-associate-rf-cuny-institute-for-justice-and-opportunity-new-york</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Elevate Nonprofits of Southwestern Pennsylvania Inc.</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 38.50/hour</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c66bddd0c644253ba0f54b97cc60e9f-finance-manager-elevate-nonprofits-of-southwestern-pennsylvania-inc-pittsburgh</t>
+  </si>
+  <si>
+    <t>Freelance Campaign Planning and Coaching Facilitator</t>
+  </si>
+  <si>
+    <t>Leave it in the Ground Initiative (LINGO)</t>
+  </si>
+  <si>
+    <t>USD 800.00 - 1000.00/day</t>
+  </si>
+  <si>
+    <t>Climate Change, Human Rights Civil Liberties, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2394922d7a2447f5a6de583166cbeb48-freelance-campaign-planning-and-coaching-facilitator-leave-it-in-the-ground-initiative-lingo-radebeul</t>
+  </si>
+  <si>
+    <t>Grants Administration Specialist</t>
+  </si>
+  <si>
+    <t>American Council on Education</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59362673979e42d5a663c2168a1b0df9-grants-administration-specialist-american-council-on-education-washington</t>
+  </si>
+  <si>
+    <t>Maryland Hall</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/262cab1636a44be08653a165b5a6ad40-human-resources-generalist-maryland-hall-annapolis</t>
+  </si>
+  <si>
     <t>International Director 2027</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 100.00 - 200.00/month</t>
   </si>
   <si>
@@ -59,6 +1310,618 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/21f5f660f5324af2b3985b5981ce7c7b-international-director-2027-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Manager – Communications (EU Programmes)</t>
+  </si>
+  <si>
+    <t>Global Resilient Cities Network</t>
+  </si>
+  <si>
+    <t>Remote (NL)</t>
+  </si>
+  <si>
+    <t>EUR 48000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Disaster Relief, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3ddb2b27ea64ddbb08ee40460da1ec9-manager-communications-eu-programmes-global-resilient-cities-network-amsterdam</t>
+  </si>
+  <si>
+    <t>Manager of Corporate Partnerships and Events</t>
+  </si>
+  <si>
+    <t>The Opportunity Network</t>
+  </si>
+  <si>
+    <t>USD 70433.00 - 77250.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b628fb307a1049f0a63ab87c5543c133-manager-of-corporate-partnerships-and-events-the-opportunity-network-new-york</t>
+  </si>
+  <si>
+    <t>Meetings Coordinator</t>
+  </si>
+  <si>
+    <t>The Association of American Law Schools</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2afa01845c524bbcb3c445c3964a0f6f-meetings-coordinator-the-association-of-american-law-schools-washington</t>
+  </si>
+  <si>
+    <t>Mission NOVA Site Director</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8bbfcee5f0e4d4ab81be3c44844cec9-mission-nova-site-director-central-union-mission-arlington</t>
+  </si>
+  <si>
+    <t>Operations &amp; Development Associate (Part-Time, Contract)</t>
+  </si>
+  <si>
+    <t>ARC - Artists at Risk Connection, Inc.</t>
+  </si>
+  <si>
+    <t>USD 4000.00 - 4500.00/month</t>
+  </si>
+  <si>
+    <t>Arts Music, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/261060229424473ab11ab91fd4133b07-operations-development-associate-part-time-contract-arc-artists-at-risk-connection-inc-new-york</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: ELEMENTARY CLASSROOM TEACHER: 2nd, 3rd or 4th-5th GRADE (NATIVE LEVEL OF ENGLISH PROFICIENCY REQUIRED)</t>
+  </si>
+  <si>
+    <t>Colegio Americano del Sur</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Escuintla, GT</t>
+  </si>
+  <si>
+    <t>USD 18000.00 - 20000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c198c13ed4344b6fa44e592cb9d103d6-opportunity-elementary-classroom-teacher-2nd-3rd-or-4th-5th-grade-native-level-of-english-proficiency-required-colegio-americano-del-sur-santa-lucia</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: HIGH LEVEL ENGLISH PROFICIENT, CERTIFIED High School English Language Arts Classroom (Teacher/Fellow) (Including school related activity involvement)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ES, GT</t>
+  </si>
+  <si>
+    <t>USD 1800.00 - 2000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0e3f3f447044b76a92e1e0cf34bf90f-opportunity-high-level-english-proficient-certified-high-school-english-language-arts-classroom-teacherfellow-including-school-related-activity-involvement-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: Middle School Social Studies/English Classroom Teacher (High Level of English Proficiency Speaker required.)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ESCUINTLA, GT</t>
+  </si>
+  <si>
+    <t>Science Technology, Rural Areas, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/071653699fff4e35b43bdc2afbc7c28b-opportunity-middle-school-social-studiesenglish-classroom-teacher-high-level-of-english-proficiency-speaker-required-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>Outreach and Training Coordinator</t>
+  </si>
+  <si>
+    <t>CASA Youth Advocates, Inc. serving Delaware and Chester Counties</t>
+  </si>
+  <si>
+    <t>Media, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ede8189f1c004339bb760fdd55a1d847-outreach-and-training-coordinator-casa-youth-advocates-inc-serving-delaware-and-chester-counties-media</t>
+  </si>
+  <si>
+    <t>Preschool Teacher</t>
+  </si>
+  <si>
+    <t>Japanese Community Youth Council</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d63bd24cc39b4961ad6bd9761d930c50-preschool-teacher-japanese-community-youth-council-san-francisco</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>TRAILS</t>
+  </si>
+  <si>
+    <t>USD 127155.00 - 134219.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c63e10768daf41309b265a34da494300-product-manager-trails-ann-arbor</t>
+  </si>
+  <si>
+    <t>Program &amp; Learner Services Coordinator</t>
+  </si>
+  <si>
+    <t>New Lehrhaus</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 33.50/hour</t>
+  </si>
+  <si>
+    <t>Education, Arts Music, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/325428ccbe50422d8d5212ce47613d01-program-learner-services-coordinator-new-lehrhaus-oakland</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Walking Softer</t>
+  </si>
+  <si>
+    <t>Newport Beach, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f43afb0151c476b863aace8fa672e85-program-coordinator-walking-softer-newport-beach</t>
+  </si>
+  <si>
+    <t>Program Coordinator, MI Mobility Fellows Program (Temporary/Part-Time)</t>
+  </si>
+  <si>
+    <t>Community Economic Development Association of Michigan (CEDAM)</t>
+  </si>
+  <si>
+    <t>Lansing, MI</t>
+  </si>
+  <si>
+    <t>USD 25.75 - 25.75/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd3f759d606149dd9d7b4231fe0e5318-program-coordinator-mi-mobility-fellows-program-temporarypart-time-community-economic-development-association-of-michigan-cedam-lansing</t>
+  </si>
+  <si>
+    <t>Program Director - Urban Institute of Mathematics</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7488b0138c1841c9b78b336e04287799-program-director-urban-institute-of-mathematics-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Program Director, JCC Maccabi®</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/508c34ebe4e7420c8db7fb3d56b6b64d-program-director-jcc-maccabi-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Program Officer</t>
+  </si>
+  <si>
+    <t>Geraldine R. Dodge Foundation</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cddd3846c1a4107ad3356bdb3552ae5-program-officer-geraldine-r-dodge-foundation-newark</t>
+  </si>
+  <si>
+    <t>PROJECT DIRECTOR, DC JAIL AND PRISON ADVOCACY PROJECT</t>
+  </si>
+  <si>
+    <t>Disability Rights DC at University Legal Services</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec7dfeb25a364cf9a97d3893e6b7b2c8-project-director-dc-jail-and-prison-advocacy-project-disability-rights-dc-at-university-legal-services-washington</t>
+  </si>
+  <si>
+    <t>Property Operations Coordinator</t>
+  </si>
+  <si>
+    <t>College for Social Innovation</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73e4846186344d788ea81fb01d710226-property-operations-coordinator-college-for-social-innovation-boston</t>
+  </si>
+  <si>
+    <t>Psiquiatra en Tapachula, Chiapas</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>Tapachula de Córdova y Ordóñez, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 46888.00 - 46888.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a67059c761d8446687c87b7bb96e6361-psiquiatra-en-tapachula-chiapas-medicos-sin-fronteras-en-mexico-ac-tapachula-de-cordova-y-ordonez</t>
+  </si>
+  <si>
+    <t>Real Estate Attorney for Nonprofit/Tax-Exempt Organizations (part-time)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1739cc1d69c740818ec910f91312912c-real-estate-attorney-for-nonprofittax-exempt-organizations-part-time-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Reentry Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55ab77f6bff840b58951a355b532924a-reentry-advocate-disability-rights-dc-at-university-legal-services-washington</t>
+  </si>
+  <si>
+    <t>Salesforce and Application Support Specialist</t>
+  </si>
+  <si>
+    <t>AO North America, Inc.</t>
+  </si>
+  <si>
+    <t>King of Prussia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cae3464a27eb48c7b7cc194f26c29f04-salesforce-and-application-support-specialist-ao-north-america-inc-king-of-prussia</t>
+  </si>
+  <si>
+    <t>Senior Data Analyst</t>
+  </si>
+  <si>
+    <t>Amaro Science</t>
+  </si>
+  <si>
+    <t>USD 102062.00 - 158178.00/year</t>
+  </si>
+  <si>
+    <t>Education, Policy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/30435a0b1b134d98945f91a961490788-senior-data-analyst-amaro-science-washington</t>
+  </si>
+  <si>
+    <t>Senior Fellow, Financial Services and Insurance Policy</t>
+  </si>
+  <si>
+    <t>R Street Institute</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b38f9fd6dce43c6b92f592e4ebeb0d6-senior-fellow-financial-services-and-insurance-policy-r-street-institute-washington</t>
+  </si>
+  <si>
+    <t>Senior Human Resources Specialist - Recovery Services Bureau</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc97590a91524d2380966da7b849bf82-senior-human-resources-specialist-recovery-services-bureau-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Senior Monitoring, Evaluation &amp; Learning Officer</t>
+  </si>
+  <si>
+    <t>Outright International</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2aa945c716cc4db2bb9ab60b742a3f00-senior-monitoring-evaluation-learning-officer-outright-international-new-york</t>
+  </si>
+  <si>
+    <t>Senior Program Manager</t>
+  </si>
+  <si>
+    <t>Global Growers Network</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7188c44c418942c5aa0b03bb253a0c74-senior-program-manager-global-growers-network-decatur</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Texas Defender Service</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62d68938caab43acba69e06f4ee07ead-senior-staff-attorney-texas-defender-service-austin</t>
+  </si>
+  <si>
+    <t>SFRRN Program Manager</t>
+  </si>
+  <si>
+    <t>Asian Americans for Civil Rights and Equality (AACRE)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2165f041705749c7a46542f6c1e50638-sfrrn-program-manager-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
+  </si>
+  <si>
+    <t>Social Worker, Adoptive Parent Services</t>
+  </si>
+  <si>
+    <t>Spence-Chapin Services to Families and Children</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edcd81b12b714f91bcc682cc510c904d-social-worker-adoptive-parent-services-spence-chapin-services-to-families-and-children-new-york</t>
+  </si>
+  <si>
+    <t>ssistant Attorney General: Real Property Bureau (3925)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/bbe287b361764a869d0cd74a4715539a-ssistant-attorney-general-real-property-bureau-3925-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
+    <t>Staff Attorney or Senior/Supervising Staff Attorney</t>
+  </si>
+  <si>
+    <t>Rutgers Immigrant Rights Clinic</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93819134b41f4e2d9181b3c8386c7f80-staff-attorney-or-seniorsupervising-staff-attorney-rutgers-immigrant-rights-clinic-newark</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Phoenix</t>
+  </si>
+  <si>
+    <t>The Young Center for Immigrant Children's Rights</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>USD 75550.80 - 86509.28/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d1da22aff1844fa8b27066cf1829d6f-staff-attorney-phoenix-the-young-center-for-immigrant-childrens-rights-phoenix</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>USD 129415.00 - 157459.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4887b4fd5a6543f4925ae174b74d7428-supervising-attorney-office-of-the-appellate-defender-new-york</t>
+  </si>
+  <si>
+    <t>Talent Operations Specialist</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3c2848a127534d4f8ef1b72041af6a5a-talent-operations-specialist-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
+    <t>Temporary Organizer</t>
+  </si>
+  <si>
+    <t>Safety Net Project - Urban Justice Center</t>
+  </si>
+  <si>
+    <t>USD 63240.00 - 72970.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ed9946e44f34b23b5d4d161683e9d88-temporary-organizer-safety-net-project-urban-justice-center-new-york</t>
+  </si>
+  <si>
+    <t>Trauma Therapist - 60% Full-Time - Counseling Center</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>USD 29.67 - 32.69/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e0eff59479a47178cca2c66076265f9-trauma-therapist-60-full-time-counseling-center-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Vice President – Global Programs &amp; Grants Management</t>
+  </si>
+  <si>
+    <t>Wadhwani Foundation</t>
+  </si>
+  <si>
+    <t>USD 300000.00 - 350000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/808b3051a45a43bab1cff3b3f6e3a92a-vice-president-global-programs-grants-management-wadhwani-foundation-los-gatos</t>
+  </si>
+  <si>
+    <t>Volunteer Manager, Engagement and Retention</t>
+  </si>
+  <si>
+    <t>Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c59cad63d3d84bfab564d6f21495ae83-volunteer-manager-engagement-and-retention-the-good-dog-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Watershed Intelligence Manager</t>
+  </si>
+  <si>
+    <t>Pioneers of our Time</t>
+  </si>
+  <si>
+    <t>Albanyà, Cataluña, ES</t>
+  </si>
+  <si>
+    <t>EUR 30000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50f7ed7be9da4172a6228235edf3fc74-watershed-intelligence-manager-pioneers-of-our-time-albanya</t>
+  </si>
+  <si>
+    <t>Writer, Brand and Editorial</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Media, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6030db589ab645939e7e22a77fc1b525-writer-brand-and-editorial-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>Youth Workshop Facilitator</t>
+  </si>
+  <si>
+    <t>Wise Young Builders</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87c564bd55bb46e1b186caabad432cf0-youth-workshop-facilitator-wise-young-builders-washington</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,62 +2346,904 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" t="s">
+        <v>146</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" t="s">
+        <v>166</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" t="s">
+        <v>200</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>201</v>
+      </c>
+      <c r="F36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -581,31 +3286,2073 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" t="s">
+        <v>255</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" t="s">
+        <v>275</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F12" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" t="s">
+        <v>298</v>
+      </c>
+      <c r="F15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" t="s">
+        <v>308</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" t="s">
+        <v>313</v>
+      </c>
+      <c r="F18" t="s">
+        <v>226</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D19" t="s">
+        <v>317</v>
+      </c>
+      <c r="E19" t="s">
+        <v>318</v>
+      </c>
+      <c r="F19" t="s">
+        <v>319</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" t="s">
+        <v>324</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E21" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" t="s">
+        <v>330</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D22" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" t="s">
+        <v>225</v>
+      </c>
+      <c r="F22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F23" t="s">
+        <v>340</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" t="s">
+        <v>343</v>
+      </c>
+      <c r="C24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F25" t="s">
+        <v>350</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>352</v>
+      </c>
+      <c r="B26" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F26" t="s">
+        <v>226</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>357</v>
+      </c>
+      <c r="B27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" t="s">
+        <v>359</v>
+      </c>
+      <c r="D27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" t="s">
+        <v>360</v>
+      </c>
+      <c r="F27" t="s">
+        <v>239</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" t="s">
+        <v>224</v>
+      </c>
+      <c r="E28" t="s">
+        <v>365</v>
+      </c>
+      <c r="F28" t="s">
+        <v>366</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B29" t="s">
+        <v>369</v>
+      </c>
+      <c r="C29" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" t="s">
+        <v>224</v>
+      </c>
+      <c r="E29" t="s">
+        <v>370</v>
+      </c>
+      <c r="F29" t="s">
+        <v>371</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B30" t="s">
+        <v>374</v>
+      </c>
+      <c r="C30" t="s">
+        <v>375</v>
+      </c>
+      <c r="D30" t="s">
+        <v>376</v>
+      </c>
+      <c r="E30" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" t="s">
+        <v>226</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" t="s">
+        <v>317</v>
+      </c>
+      <c r="E31" t="s">
+        <v>238</v>
+      </c>
+      <c r="F31" t="s">
+        <v>280</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>381</v>
+      </c>
+      <c r="B32" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32" t="s">
+        <v>383</v>
+      </c>
+      <c r="D32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" t="s">
+        <v>384</v>
+      </c>
+      <c r="F32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" t="s">
+        <v>388</v>
+      </c>
+      <c r="C33" t="s">
+        <v>389</v>
+      </c>
+      <c r="D33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" t="s">
+        <v>390</v>
+      </c>
+      <c r="F33" t="s">
+        <v>391</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" t="s">
+        <v>393</v>
+      </c>
+      <c r="C34" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" t="s">
+        <v>395</v>
+      </c>
+      <c r="F34" t="s">
+        <v>396</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>398</v>
+      </c>
+      <c r="B35" t="s">
+        <v>399</v>
+      </c>
+      <c r="C35" t="s">
+        <v>400</v>
+      </c>
+      <c r="D35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F35" t="s">
+        <v>402</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>404</v>
+      </c>
+      <c r="B36" t="s">
+        <v>405</v>
+      </c>
+      <c r="C36" t="s">
+        <v>259</v>
+      </c>
+      <c r="D36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" t="s">
+        <v>323</v>
+      </c>
+      <c r="F36" t="s">
+        <v>406</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>408</v>
+      </c>
+      <c r="B37" t="s">
+        <v>409</v>
+      </c>
+      <c r="C37" t="s">
+        <v>223</v>
+      </c>
+      <c r="D37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E37" t="s">
+        <v>410</v>
+      </c>
+      <c r="F37" t="s">
+        <v>411</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>413</v>
+      </c>
+      <c r="B38" t="s">
+        <v>414</v>
+      </c>
+      <c r="C38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" t="s">
+        <v>376</v>
+      </c>
+      <c r="E38" t="s">
+        <v>415</v>
+      </c>
+      <c r="F38" t="s">
+        <v>416</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39" t="s">
+        <v>419</v>
+      </c>
+      <c r="C39" t="s">
+        <v>273</v>
+      </c>
+      <c r="D39" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39" t="s">
+        <v>420</v>
+      </c>
+      <c r="F39" t="s">
+        <v>371</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
+        <v>422</v>
+      </c>
+      <c r="C40" t="s">
+        <v>423</v>
+      </c>
+      <c r="D40" t="s">
+        <v>317</v>
+      </c>
+      <c r="E40" t="s">
+        <v>424</v>
+      </c>
+      <c r="F40" t="s">
+        <v>425</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>427</v>
+      </c>
+      <c r="B41" t="s">
+        <v>428</v>
+      </c>
+      <c r="C41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" t="s">
+        <v>376</v>
+      </c>
+      <c r="E41" t="s">
+        <v>429</v>
+      </c>
+      <c r="F41" t="s">
+        <v>430</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>432</v>
+      </c>
+      <c r="B42" t="s">
+        <v>433</v>
+      </c>
+      <c r="C42" t="s">
+        <v>434</v>
+      </c>
+      <c r="D42" t="s">
+        <v>224</v>
+      </c>
+      <c r="E42" t="s">
+        <v>435</v>
+      </c>
+      <c r="F42" t="s">
+        <v>436</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>438</v>
+      </c>
+      <c r="B43" t="s">
+        <v>439</v>
+      </c>
+      <c r="C43" t="s">
+        <v>236</v>
+      </c>
+      <c r="D43" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" t="s">
+        <v>440</v>
+      </c>
+      <c r="F43" t="s">
+        <v>441</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>443</v>
+      </c>
+      <c r="B44" t="s">
+        <v>444</v>
+      </c>
+      <c r="C44" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" t="s">
+        <v>224</v>
+      </c>
+      <c r="E44" t="s">
+        <v>445</v>
+      </c>
+      <c r="F44" t="s">
+        <v>446</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>448</v>
+      </c>
+      <c r="B45" t="s">
+        <v>449</v>
+      </c>
+      <c r="C45" t="s">
+        <v>364</v>
+      </c>
+      <c r="D45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" t="s">
+        <v>450</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>452</v>
+      </c>
+      <c r="B46" t="s">
+        <v>453</v>
+      </c>
+      <c r="C46" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" t="s">
+        <v>376</v>
+      </c>
+      <c r="E46" t="s">
+        <v>454</v>
+      </c>
+      <c r="F46" t="s">
+        <v>455</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>457</v>
+      </c>
+      <c r="B47" t="s">
+        <v>458</v>
+      </c>
+      <c r="C47" t="s">
+        <v>459</v>
+      </c>
+      <c r="D47" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" t="s">
+        <v>460</v>
+      </c>
+      <c r="F47" t="s">
+        <v>226</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>462</v>
+      </c>
+      <c r="B48" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" t="s">
+        <v>463</v>
+      </c>
+      <c r="D48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" t="s">
+        <v>464</v>
+      </c>
+      <c r="F48" t="s">
+        <v>465</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>467</v>
+      </c>
+      <c r="B49" t="s">
+        <v>458</v>
+      </c>
+      <c r="C49" t="s">
+        <v>468</v>
+      </c>
+      <c r="D49" t="s">
+        <v>224</v>
+      </c>
+      <c r="E49" t="s">
+        <v>460</v>
+      </c>
+      <c r="F49" t="s">
+        <v>469</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>471</v>
+      </c>
+      <c r="B50" t="s">
+        <v>472</v>
+      </c>
+      <c r="C50" t="s">
+        <v>473</v>
+      </c>
+      <c r="D50" t="s">
+        <v>224</v>
+      </c>
+      <c r="E50" t="s">
+        <v>474</v>
+      </c>
+      <c r="F50" t="s">
+        <v>475</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>477</v>
+      </c>
+      <c r="B51" t="s">
+        <v>478</v>
+      </c>
+      <c r="C51" t="s">
+        <v>479</v>
+      </c>
+      <c r="D51" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" t="s">
+        <v>480</v>
+      </c>
+      <c r="F51" t="s">
+        <v>481</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>483</v>
+      </c>
+      <c r="B52" t="s">
+        <v>484</v>
+      </c>
+      <c r="C52" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" t="s">
+        <v>485</v>
+      </c>
+      <c r="F52" t="s">
+        <v>486</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>488</v>
+      </c>
+      <c r="B53" t="s">
+        <v>489</v>
+      </c>
+      <c r="C53" t="s">
+        <v>490</v>
+      </c>
+      <c r="D53" t="s">
+        <v>224</v>
+      </c>
+      <c r="E53" t="s">
+        <v>491</v>
+      </c>
+      <c r="F53" t="s">
+        <v>492</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>494</v>
+      </c>
+      <c r="B54" t="s">
+        <v>495</v>
+      </c>
+      <c r="C54" t="s">
+        <v>496</v>
+      </c>
+      <c r="D54" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" t="s">
+        <v>497</v>
+      </c>
+      <c r="F54" t="s">
+        <v>498</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>500</v>
+      </c>
+      <c r="B55" t="s">
+        <v>501</v>
+      </c>
+      <c r="C55" t="s">
+        <v>502</v>
+      </c>
+      <c r="D55" t="s">
+        <v>237</v>
+      </c>
+      <c r="E55" t="s">
+        <v>503</v>
+      </c>
+      <c r="F55" t="s">
+        <v>504</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>506</v>
+      </c>
+      <c r="B56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" t="s">
+        <v>243</v>
+      </c>
+      <c r="D56" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" t="s">
+        <v>323</v>
+      </c>
+      <c r="F56" t="s">
+        <v>245</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>508</v>
+      </c>
+      <c r="B57" t="s">
+        <v>509</v>
+      </c>
+      <c r="C57" t="s">
+        <v>259</v>
+      </c>
+      <c r="D57" t="s">
+        <v>224</v>
+      </c>
+      <c r="E57" t="s">
+        <v>510</v>
+      </c>
+      <c r="F57" t="s">
+        <v>511</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>513</v>
+      </c>
+      <c r="B58" t="s">
+        <v>514</v>
+      </c>
+      <c r="C58" t="s">
+        <v>515</v>
+      </c>
+      <c r="D58" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58" t="s">
+        <v>516</v>
+      </c>
+      <c r="F58" t="s">
+        <v>402</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>518</v>
+      </c>
+      <c r="B59" t="s">
+        <v>519</v>
+      </c>
+      <c r="C59" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" t="s">
+        <v>224</v>
+      </c>
+      <c r="E59" t="s">
+        <v>520</v>
+      </c>
+      <c r="F59" t="s">
+        <v>521</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>523</v>
+      </c>
+      <c r="B60" t="s">
+        <v>524</v>
+      </c>
+      <c r="C60" t="s">
+        <v>297</v>
+      </c>
+      <c r="D60" t="s">
+        <v>224</v>
+      </c>
+      <c r="E60" t="s">
+        <v>525</v>
+      </c>
+      <c r="F60" t="s">
+        <v>526</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>528</v>
+      </c>
+      <c r="B61" t="s">
+        <v>529</v>
+      </c>
+      <c r="C61" t="s">
+        <v>530</v>
+      </c>
+      <c r="D61" t="s">
+        <v>224</v>
+      </c>
+      <c r="E61" t="s">
+        <v>531</v>
+      </c>
+      <c r="F61" t="s">
+        <v>308</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>533</v>
+      </c>
+      <c r="B62" t="s">
+        <v>379</v>
+      </c>
+      <c r="C62" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" t="s">
+        <v>317</v>
+      </c>
+      <c r="E62" t="s">
+        <v>238</v>
+      </c>
+      <c r="F62" t="s">
+        <v>280</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>535</v>
+      </c>
+      <c r="B63" t="s">
+        <v>519</v>
+      </c>
+      <c r="C63" t="s">
+        <v>273</v>
+      </c>
+      <c r="D63" t="s">
+        <v>224</v>
+      </c>
+      <c r="E63" t="s">
+        <v>323</v>
+      </c>
+      <c r="F63" t="s">
+        <v>521</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>537</v>
+      </c>
+      <c r="B64" t="s">
+        <v>538</v>
+      </c>
+      <c r="C64" t="s">
+        <v>539</v>
+      </c>
+      <c r="D64" t="s">
+        <v>224</v>
+      </c>
+      <c r="E64" t="s">
+        <v>540</v>
+      </c>
+      <c r="F64" t="s">
+        <v>541</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>543</v>
+      </c>
+      <c r="B65" t="s">
+        <v>544</v>
+      </c>
+      <c r="C65" t="s">
+        <v>273</v>
+      </c>
+      <c r="D65" t="s">
+        <v>224</v>
+      </c>
+      <c r="E65" t="s">
+        <v>545</v>
+      </c>
+      <c r="F65" t="s">
+        <v>546</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>548</v>
+      </c>
+      <c r="B66" t="s">
+        <v>549</v>
+      </c>
+      <c r="C66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66" t="s">
+        <v>550</v>
+      </c>
+      <c r="F66" t="s">
+        <v>350</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>552</v>
+      </c>
+      <c r="B67" t="s">
+        <v>553</v>
+      </c>
+      <c r="C67" t="s">
+        <v>297</v>
+      </c>
+      <c r="D67" t="s">
+        <v>224</v>
+      </c>
+      <c r="E67" t="s">
+        <v>554</v>
+      </c>
+      <c r="F67" t="s">
+        <v>555</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>557</v>
+      </c>
+      <c r="B68" t="s">
+        <v>558</v>
+      </c>
+      <c r="C68" t="s">
+        <v>223</v>
+      </c>
+      <c r="D68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E68" t="s">
+        <v>226</v>
+      </c>
+      <c r="F68" t="s">
+        <v>559</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>561</v>
+      </c>
+      <c r="B69" t="s">
+        <v>562</v>
+      </c>
+      <c r="C69" t="s">
+        <v>359</v>
+      </c>
+      <c r="D69" t="s">
+        <v>224</v>
+      </c>
+      <c r="E69" t="s">
+        <v>563</v>
+      </c>
+      <c r="F69" t="s">
+        <v>564</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>566</v>
+      </c>
+      <c r="B70" t="s">
+        <v>567</v>
+      </c>
+      <c r="C70" t="s">
+        <v>568</v>
+      </c>
+      <c r="D70" t="s">
+        <v>224</v>
+      </c>
+      <c r="E70" t="s">
+        <v>569</v>
+      </c>
+      <c r="F70" t="s">
+        <v>280</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>571</v>
+      </c>
+      <c r="B71" t="s">
+        <v>572</v>
+      </c>
+      <c r="C71" t="s">
+        <v>479</v>
+      </c>
+      <c r="D71" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" t="s">
+        <v>573</v>
+      </c>
+      <c r="F71" t="s">
+        <v>574</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>576</v>
+      </c>
+      <c r="B72" t="s">
+        <v>577</v>
+      </c>
+      <c r="C72" t="s">
+        <v>259</v>
+      </c>
+      <c r="D72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72" t="s">
+        <v>578</v>
+      </c>
+      <c r="F72" t="s">
+        <v>579</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>581</v>
+      </c>
+      <c r="B73" t="s">
+        <v>582</v>
+      </c>
+      <c r="C73" t="s">
+        <v>583</v>
+      </c>
+      <c r="D73" t="s">
+        <v>224</v>
+      </c>
+      <c r="E73" t="s">
+        <v>226</v>
+      </c>
+      <c r="F73" t="s">
+        <v>226</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>585</v>
+      </c>
+      <c r="B74" t="s">
+        <v>586</v>
+      </c>
+      <c r="C74" t="s">
+        <v>587</v>
+      </c>
+      <c r="D74" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" t="s">
+        <v>588</v>
+      </c>
+      <c r="F74" t="s">
+        <v>589</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>591</v>
+      </c>
+      <c r="B75" t="s">
+        <v>592</v>
+      </c>
+      <c r="C75" t="s">
+        <v>593</v>
+      </c>
+      <c r="D75" t="s">
+        <v>224</v>
+      </c>
+      <c r="E75" t="s">
+        <v>594</v>
+      </c>
+      <c r="F75" t="s">
+        <v>595</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>597</v>
+      </c>
+      <c r="B76" t="s">
+        <v>278</v>
+      </c>
+      <c r="C76" t="s">
+        <v>259</v>
+      </c>
+      <c r="D76" t="s">
+        <v>224</v>
+      </c>
+      <c r="E76" t="s">
+        <v>598</v>
+      </c>
+      <c r="F76" t="s">
+        <v>280</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>600</v>
+      </c>
+      <c r="B77" t="s">
+        <v>264</v>
+      </c>
+      <c r="C77" t="s">
+        <v>259</v>
+      </c>
+      <c r="D77" t="s">
+        <v>224</v>
+      </c>
+      <c r="E77" t="s">
+        <v>601</v>
+      </c>
+      <c r="F77" t="s">
+        <v>226</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>603</v>
+      </c>
+      <c r="B78" t="s">
+        <v>604</v>
+      </c>
+      <c r="C78" t="s">
+        <v>259</v>
+      </c>
+      <c r="D78" t="s">
+        <v>285</v>
+      </c>
+      <c r="E78" t="s">
+        <v>605</v>
+      </c>
+      <c r="F78" t="s">
+        <v>606</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>608</v>
+      </c>
+      <c r="B79" t="s">
+        <v>609</v>
+      </c>
+      <c r="C79" t="s">
+        <v>259</v>
+      </c>
+      <c r="D79" t="s">
+        <v>317</v>
+      </c>
+      <c r="E79" t="s">
+        <v>610</v>
+      </c>
+      <c r="F79" t="s">
+        <v>611</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>613</v>
+      </c>
+      <c r="B80" t="s">
+        <v>614</v>
+      </c>
+      <c r="C80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D80" t="s">
+        <v>224</v>
+      </c>
+      <c r="E80" t="s">
+        <v>615</v>
+      </c>
+      <c r="F80" t="s">
+        <v>385</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>617</v>
+      </c>
+      <c r="B81" t="s">
+        <v>268</v>
+      </c>
+      <c r="C81" t="s">
+        <v>223</v>
+      </c>
+      <c r="D81" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" t="s">
+        <v>254</v>
+      </c>
+      <c r="F81" t="s">
+        <v>618</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>620</v>
+      </c>
+      <c r="B82" t="s">
+        <v>621</v>
+      </c>
+      <c r="C82" t="s">
+        <v>622</v>
+      </c>
+      <c r="D82" t="s">
+        <v>224</v>
+      </c>
+      <c r="E82" t="s">
+        <v>623</v>
+      </c>
+      <c r="F82" t="s">
+        <v>624</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>626</v>
+      </c>
+      <c r="B83" t="s">
+        <v>627</v>
+      </c>
+      <c r="C83" t="s">
+        <v>223</v>
+      </c>
+      <c r="D83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" t="s">
+        <v>628</v>
+      </c>
+      <c r="F83" t="s">
+        <v>629</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>631</v>
+      </c>
+      <c r="B84" t="s">
+        <v>632</v>
+      </c>
+      <c r="C84" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" t="s">
+        <v>376</v>
+      </c>
+      <c r="E84" t="s">
+        <v>633</v>
+      </c>
+      <c r="F84" t="s">
+        <v>634</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-29.xlsx
+++ b/docs/xlsx/jobs-2026-10-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="877">
   <si>
     <t>Title</t>
   </si>
@@ -700,6 +700,27 @@
     <t>https://www.idealist.org/en/consultant-job/71173879db8346de998379c9278d59a4-accountant-remote-fohrman-fohrman-inc-dana-point</t>
   </si>
   <si>
+    <t>Administrative Assistant (Part-Time)</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist Church of Berkeley</t>
+  </si>
+  <si>
+    <t>Kensington, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8215c6994554d2cb01a852a4f718b78-administrative-assistant-part-time-unitarian-universalist-church-of-berkeley-kensington</t>
+  </si>
+  <si>
     <t>Administrative Assistant, Immigration Practice</t>
   </si>
   <si>
@@ -739,6 +760,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/287ada512aff4c968bfd0aceff1c46d3-algebra-i-and-ii-instructors-after-school-liberty-leads-liberty-leads-in-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Assistant Attorney General: Real Property Bureau (3925)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186494.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/bbe287b361764a869d0cd74a4715539a-assistant-attorney-general-real-property-bureau-3925-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
     <t>Assistant Director - Urban Institute of Mathematics</t>
   </si>
   <si>
@@ -757,6 +793,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/539c130d02e84cc9935a7c4f9f49b43d-assistant-director-urban-institute-of-mathematics-east-side-house-settlement-bronx-county</t>
   </si>
   <si>
+    <t>Assistant General Counsel</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c8541ac297f4dcda6461144f64c05c1-assistant-general-counsel-the-public-interest-network-denver</t>
+  </si>
+  <si>
     <t>ASSOC VICE CHANCELLOR-FINANCE &amp; OPERATIONS (CCC FOUNDATION)</t>
   </si>
   <si>
@@ -805,6 +859,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/2b4fc5d7e561483b905431bcae70c659-associate-director-of-real-estate-pswrx-new-york</t>
   </si>
   <si>
+    <t>Attorney, Federal Immigration Litigation, Immigration Practice</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 123000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9a1bc27a4b84ee6b964de989db154a0-attorney-federal-immigration-litigation-immigration-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Budget Analyst</t>
   </si>
   <si>
@@ -829,15 +892,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/299dbcf9aae143408b248f76dedf98e6-business-development-manager-the-good-dog-foundation-new-york</t>
   </si>
   <si>
+    <t>California Organizing Manager</t>
+  </si>
+  <si>
+    <t>Mothers Against Media Addiction (MAMA)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Consumer Protection, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8f3be599e054d8f85646f5d9785f926-california-organizing-manager-mothers-against-media-addiction-mama-new-york</t>
+  </si>
+  <si>
+    <t>Campaigner for Environmental Non Profit</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Wilmington, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef0a2baeab834e288f5c4ae1f470111b-campaigner-for-environmental-non-profit-green-corps-wilmington</t>
+  </si>
+  <si>
+    <t>Virginia Beach, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2de1410e5424df0a587d89dc1e478f5-campaigner-for-environmental-non-profit-green-corps-virginia-beach</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c506a69c53fc41ba9b07faa25f457d8c-campaigner-for-environmental-non-profit-green-corps-denver</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7129cbe5bb574f4da118446ae13e5d35-campaigner-for-environmental-non-profit-green-corps-columbus</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3be11f8791d44af2bc6c946d1100638d-campaigner-for-environmental-non-profit-green-corps-boston</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e11eed4cee84ee89d3eb92bda67688e-campaigner-for-environmental-non-profit-green-corps-washington</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/085cf0b1258e414cb0b3cfde7ac624ed-campaigner-for-environmental-non-profit-green-corps-portland</t>
+  </si>
+  <si>
+    <t>Cantonese/Mandarin Speaker Social Worker, Diana Jones SC</t>
+  </si>
+  <si>
+    <t>RiseBoro Community Partnership</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 71326.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a9c2d3155f24093b2787dc7fb933597-cantonesemandarin-speaker-social-worker-diana-jones-sc-riseboro-community-partnership-kings-county</t>
+  </si>
+  <si>
     <t>Chief of Partnerships</t>
   </si>
   <si>
     <t>World Justice Project</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 136500.00 - 230000.00/year</t>
   </si>
   <si>
@@ -847,6 +997,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/9f0c77cde6c44e63a5a9547cf0e95d16-chief-of-partnerships-world-justice-project-washington</t>
   </si>
   <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>The YWCA of the City of New York</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Volunteering, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f6c8597729e4d5cb4995e5897fdff53-chief-operating-officer-the-ywca-of-the-city-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Clean Air Campaign Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/007d0700645e402da0dc0b7a19b09fd9-clean-air-campaign-advocate-environment-america-washington</t>
+  </si>
+  <si>
     <t>Client Services Coordinator</t>
   </si>
   <si>
@@ -871,9 +1051,6 @@
     <t>Remote (District of Columbia)</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 29.00 - 32.00/hour</t>
   </si>
   <si>
@@ -907,9 +1084,6 @@
     <t>Positive Tracks</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 73500.00 - 73500.00/year</t>
   </si>
   <si>
@@ -919,6 +1093,27 @@
     <t>https://www.idealist.org/en/government-job/f309418436264dea95c1488224b768d7-community-engagement-manager-boston-positive-tracks-boston</t>
   </si>
   <si>
+    <t>Community Field Representative – Energy Outreach (Scranton / Wilkes-Barre)</t>
+  </si>
+  <si>
+    <t>Rosales Communications</t>
+  </si>
+  <si>
+    <t>Scranton, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/12ba5c2091d049c29a28372a0ded0c3b-community-field-representative-energy-outreach-scranton-wilkes-barre-rosales-communications-scranton</t>
+  </si>
+  <si>
     <t>Community Manager</t>
   </si>
   <si>
@@ -931,6 +1126,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/3c07a921c64e4d37bb37263851ab0974-community-manager-yoga-alliance-arlington</t>
   </si>
   <si>
+    <t>Community Outreach Representative</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Communications Access, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/9f0a0e0ff1cc4607be5799fde3b59e26-community-outreach-representative-rosales-communications-philadelphia</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative (Baltimore)</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1d5a881349b74dd7a218240d8e0b63da-community-outreach-representative-baltimore-rosales-communications-baltimore</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative (Energy Efficiency – Lehigh Valley)</t>
+  </si>
+  <si>
+    <t>Allentown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/9735562253c447aabdf262076ff4a576-community-outreach-representative-energy-efficiency-lehigh-valley-rosales-communications-allentown</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative (Energy Efficiency Outreach — Harrisburg, PA)</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a6da51320d054c7fbb4652a9001ac02a-community-outreach-representative-energy-efficiency-outreach-harrisburg-pa-rosales-communications-harrisburg</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -967,9 +1207,6 @@
     <t>Friends of the Jerusalem Youth Chorus</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 27.00 - 27.00/hour</t>
   </si>
   <si>
@@ -1045,18 +1282,30 @@
     <t>Director of Development</t>
   </si>
   <si>
-    <t>Mothers Against Media Addiction (MAMA)</t>
-  </si>
-  <si>
     <t>USD 130000.00 - 140000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Consumer Protection, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/f1aebf152e7444fcaf4ccea92a1127d8-director-of-development-mothers-against-media-addiction-mama-new-york</t>
   </si>
   <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>UnCommon Law</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 126400.00 - 154050.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b910ba89fcf14b5ba5d3d61ea5ac3df5-director-of-finance-and-operations-uncommon-law-oakland</t>
+  </si>
+  <si>
     <t>Director of Grassroots Advocacy</t>
   </si>
   <si>
@@ -1078,9 +1327,6 @@
     <t>Philadelphia Association of Community Development Corporations (PACDC)</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 92000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -1096,12 +1342,60 @@
     <t>Decatur, Georgia</t>
   </si>
   <si>
-    <t>USD 80000.00 - 90000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9746ebe487c94520a6a650d0d56083f0-director-of-people-operations-global-village-project-decatur</t>
   </si>
   <si>
+    <t>Director of Policy</t>
+  </si>
+  <si>
+    <t>UCLA Latino Policy and Politics Institute</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/962a6ed648f04492a65f00beff2d21ea-director-of-policy-ucla-latino-policy-and-politics-institute-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Programming and Engagement</t>
+  </si>
+  <si>
+    <t>Keshet Dance and Center for the Arts</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce5f2a47a27649aca456a2d0e1ba3fe4-director-of-programming-and-engagement-keshet-dance-and-center-for-the-arts-albuquerque</t>
+  </si>
+  <si>
+    <t>Director of Social Services</t>
+  </si>
+  <si>
+    <t>The Ark</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/983d7b17a83b4820bd98b21547d67249-director-of-social-services-the-ark-chicago</t>
+  </si>
+  <si>
     <t>Director of Volunteer &amp; Community Engagement</t>
   </si>
   <si>
@@ -1135,6 +1429,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5aada413e804422ebdc01a506fb8da3d-director-ai-education-initiatives-ai4ccny-the-foundation-for-city-college-new-york</t>
   </si>
   <si>
+    <t>Early Childhood Clinician</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6139fe1786964ae399139c7c8f55d444-early-childhood-clinician-riseboro-community-partnership-kings-county</t>
+  </si>
+  <si>
     <t>Editor, Moldova</t>
   </si>
   <si>
@@ -1144,9 +1450,6 @@
     <t>Remote (MD)</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/49c5fc86bba344378ff5192b15133548-editor-moldova-organized-crime-and-corruption-reporting-project-amsterdam</t>
   </si>
   <si>
@@ -1159,6 +1462,21 @@
     <t>https://www.idealist.org/en/consultant-job/67800d49ceb9441ab6afc1f8bb274d2f-employment-attorney-for-nonprofittax-exempt-organizations-part-time-cheshire-law-group-philadelphia</t>
   </si>
   <si>
+    <t>Equitable Building Decarbonization Community Outreach &amp; Organizing Coordinator</t>
+  </si>
+  <si>
+    <t>Climate Action Campaign</t>
+  </si>
+  <si>
+    <t>Fullerton, California</t>
+  </si>
+  <si>
+    <t>USD 55120.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37a61554c4724de5874ebb51b87530ee-equitable-building-decarbonization-community-outreach-organizing-coordinator-climate-action-campaign-fullerton</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
@@ -1183,9 +1501,6 @@
     <t>Counterterrorism Education Learning Lab (CELL)</t>
   </si>
   <si>
-    <t>Denver, Colorado</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -1210,6 +1525,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b3eb89340da0494eb2339e5e3934cb40-executive-director-tulsa-county-medical-society-tulsa</t>
   </si>
   <si>
+    <t>Capital Development Services</t>
+  </si>
+  <si>
+    <t>Winston-Salem, North Carolina</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/262453290f054edf9c89f9035fd2d823-executive-director-capital-development-services-winston-salem</t>
+  </si>
+  <si>
     <t>Executive Director, Downtown Ashland Association</t>
   </si>
   <si>
@@ -1228,6 +1555,15 @@
     <t>https://www.idealist.org/en/government-job/1589e780f21e45deb9576a9c63fc2b8b-executive-director-downtown-ashland-association-town-of-ashland-virginia-ashland</t>
   </si>
   <si>
+    <t>Facilities Manager (Full-Time, or Two Part-Time Positions), Unitarian Universalist Church of Berkeley</t>
+  </si>
+  <si>
+    <t>USD 70305.00 - 70305.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/912c808ee5db45dd9fe8bddb1042d440-facilities-manager-full-time-or-two-part-time-positions-unitarian-universalist-church-of-berkeley-unitarian-universalist-church-of-berkeley-kensington</t>
+  </si>
+  <si>
     <t>Finance Associate</t>
   </si>
   <si>
@@ -1255,6 +1591,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0c66bddd0c644253ba0f54b97cc60e9f-finance-manager-elevate-nonprofits-of-southwestern-pennsylvania-inc-pittsburgh</t>
   </si>
   <si>
+    <t>Finance Manager - Resilient Strategies LLC</t>
+  </si>
+  <si>
+    <t>Resilient Strategies LLC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/87ed0a0dc31a440dadfff137d8b554b2-finance-manager-resilient-strategies-llc-resilient-strategies-llc-oakland</t>
+  </si>
+  <si>
     <t>Freelance Campaign Planning and Coaching Facilitator</t>
   </si>
   <si>
@@ -1270,6 +1618,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2394922d7a2447f5a6de583166cbeb48-freelance-campaign-planning-and-coaching-facilitator-leave-it-in-the-ground-initiative-lingo-radebeul</t>
   </si>
   <si>
+    <t>Giving Manager</t>
+  </si>
+  <si>
+    <t>Rain City Rock Camp</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/926e9fb3164d4d42bd4705664d27d928-giving-manager-rain-city-rock-camp-seattle</t>
+  </si>
+  <si>
     <t>Grants Administration Specialist</t>
   </si>
   <si>
@@ -1282,6 +1645,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/59362673979e42d5a663c2168a1b0df9-grants-administration-specialist-american-council-on-education-washington</t>
   </si>
   <si>
+    <t>Health Advocate</t>
+  </si>
+  <si>
+    <t>Cabrini Immigrant Services of NYC</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0fd14559e9b478f8e242fa370390e94-health-advocate-cabrini-immigrant-services-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>HR Business Partner</t>
+  </si>
+  <si>
+    <t>MissionWired</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3af74bed05214b06b022ee02bc197be9-hr-business-partner-missionwired-washington</t>
+  </si>
+  <si>
     <t>Maryland Hall</t>
   </si>
   <si>
@@ -1312,6 +1705,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/21f5f660f5324af2b3985b5981ce7c7b-international-director-2027-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Junior Research Analyst</t>
+  </si>
+  <si>
+    <t>The Policy and Research Group</t>
+  </si>
+  <si>
+    <t>New Orleans, LA</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8745096ea1b0409aac4c049b2e4b0450-junior-research-analyst-the-policy-and-research-group-new-orleans</t>
+  </si>
+  <si>
+    <t>Legislative Campaign Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9e979a2e8b2434384fde997ca54eee2-legislative-campaign-associate-us-pirg-washington</t>
+  </si>
+  <si>
     <t>Manager – Communications (EU Programmes)</t>
   </si>
   <si>
@@ -1345,6 +1768,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/b628fb307a1049f0a63ab87c5543c133-manager-of-corporate-partnerships-and-events-the-opportunity-network-new-york</t>
   </si>
   <si>
+    <t>Manager, Marketing and Content</t>
+  </si>
+  <si>
+    <t>Mid-Hudson Energy Transition</t>
+  </si>
+  <si>
+    <t>Kingston, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f3841ad70914448863b2dbf4a982f2a-manager-marketing-and-content-mid-hudson-energy-transition-kingston</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Patron Services Coordinator</t>
+  </si>
+  <si>
+    <t>Studio East Training for the Performing Arts</t>
+  </si>
+  <si>
+    <t>Kirkland, Washington</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba91c782caa24080b4c40346fbd91950-marketing-patron-services-coordinator-studio-east-training-for-the-performing-arts-kirkland</t>
+  </si>
+  <si>
+    <t>Marketing and Design Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5e53a8b7ba8492bb2c403b6095477a4-marketing-and-design-manager-rain-city-rock-camp-seattle</t>
+  </si>
+  <si>
     <t>Meetings Coordinator</t>
   </si>
   <si>
@@ -1360,6 +1825,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2afa01845c524bbcb3c445c3964a0f6f-meetings-coordinator-the-association-of-american-law-schools-washington</t>
   </si>
   <si>
+    <t>Membership Retention Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>Manassas, Virginia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bd319c484b54bab8ceddf09b8fd3479-membership-retention-specialist-girl-scout-council-of-the-nations-capital-manassas</t>
+  </si>
+  <si>
     <t>Mission NOVA Site Director</t>
   </si>
   <si>
@@ -1372,6 +1855,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/b8bbfcee5f0e4d4ab81be3c44844cec9-mission-nova-site-director-central-union-mission-arlington</t>
   </si>
   <si>
+    <t>New Hampshire Environmental Organizer</t>
+  </si>
+  <si>
+    <t>Manchester, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0992b3b0a9ae4eebbe5e859782e473f9-new-hampshire-environmental-organizer-environment-america-manchester</t>
+  </si>
+  <si>
     <t>Operations &amp; Development Associate (Part-Time, Contract)</t>
   </si>
   <si>
@@ -1387,6 +1879,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/261060229424473ab11ab91fd4133b07-operations-development-associate-part-time-contract-arc-artists-at-risk-connection-inc-new-york</t>
   </si>
   <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Friends of the Columbia Gorge</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd0d25a5c74642dc900a22ec0afb7691-operations-coordinator-friends-of-the-columbia-gorge-portland</t>
+  </si>
+  <si>
+    <t>Humin, Inc.</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Mental Health, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19862b4352484980a644c37e9d199137-operations-coordinator-humin-inc-madison</t>
+  </si>
+  <si>
     <t>OPPORTUNITY: ELEMENTARY CLASSROOM TEACHER: 2nd, 3rd or 4th-5th GRADE (NATIVE LEVEL OF ENGLISH PROFICIENCY REQUIRED)</t>
   </si>
   <si>
@@ -1429,6 +1951,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/071653699fff4e35b43bdc2afbc7c28b-opportunity-middle-school-social-studiesenglish-classroom-teacher-high-level-of-english-proficiency-speaker-required-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
   </si>
   <si>
+    <t>Oregon Healthcare Campaign Associate</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f294ae3605245278d667449072f6d61-oregon-healthcare-campaign-associate-us-pirg-portland</t>
+  </si>
+  <si>
     <t>Outreach and Training Coordinator</t>
   </si>
   <si>
@@ -1447,6 +1978,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/ede8189f1c004339bb760fdd55a1d847-outreach-and-training-coordinator-casa-youth-advocates-inc-serving-delaware-and-chester-counties-media</t>
   </si>
   <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98d8967607d548e8804d82283cfa65fa-philanthropy-officer-friends-of-the-columbia-gorge-portland</t>
+  </si>
+  <si>
     <t>Preschool Teacher</t>
   </si>
   <si>
@@ -1459,9 +1999,6 @@
     <t>USD 72000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Children Youth</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d63bd24cc39b4961ad6bd9761d930c50-preschool-teacher-japanese-community-youth-council-san-francisco</t>
   </si>
   <si>
@@ -1486,9 +2023,6 @@
     <t>New Lehrhaus</t>
   </si>
   <si>
-    <t>Oakland, California</t>
-  </si>
-  <si>
     <t>USD 30.00 - 33.50/hour</t>
   </si>
   <si>
@@ -1570,6 +2104,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6cddd3846c1a4107ad3356bdb3552ae5-program-officer-geraldine-r-dodge-foundation-newark</t>
   </si>
   <si>
+    <t>Foundation for the Mid South, Inc. (60507)</t>
+  </si>
+  <si>
+    <t>Jackson, Mississippi</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abb65989a6a4445c81e28f8b1101b963-program-officer-foundation-for-the-mid-south-inc-60507-jackson</t>
+  </si>
+  <si>
     <t>PROJECT DIRECTOR, DC JAIL AND PRISON ADVOCACY PROJECT</t>
   </si>
   <si>
@@ -1627,6 +2176,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/55ab77f6bff840b58951a355b532924a-reentry-advocate-disability-rights-dc-at-university-legal-services-washington</t>
   </si>
   <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c565ba898db9436fad0f8fd901ba78e4-research-assistant-the-policy-and-research-group-new-orleans</t>
+  </si>
+  <si>
     <t>Salesforce and Application Support Specialist</t>
   </si>
   <si>
@@ -1672,15 +2230,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/2b38f9fd6dce43c6b92f592e4ebeb0d6-senior-fellow-financial-services-and-insurance-policy-r-street-institute-washington</t>
   </si>
   <si>
+    <t>Senior HR Manager</t>
+  </si>
+  <si>
+    <t>Experience Camps</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d57fa30c5cad4ad781855f841e03dd4a-senior-hr-manager-experience-camps-westport</t>
+  </si>
+  <si>
     <t>Senior Human Resources Specialist - Recovery Services Bureau</t>
   </si>
   <si>
     <t>Boston Public Health Commission</t>
   </si>
   <si>
-    <t>USD 85000.00 - 95000.00/year</t>
-  </si>
-  <si>
     <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
   </si>
   <si>
@@ -1705,9 +2275,6 @@
     <t>Global Growers Network</t>
   </si>
   <si>
-    <t>USD 55000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Agriculture, Community Development, Hunger Food Security</t>
   </si>
   <si>
@@ -1729,6 +2296,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/62d68938caab43acba69e06f4ee07ead-senior-staff-attorney-texas-defender-service-austin</t>
   </si>
   <si>
+    <t>Senior Staff Attorney, Criminal Justice and Police Practices</t>
+  </si>
+  <si>
+    <t>ACLU - Southern California</t>
+  </si>
+  <si>
+    <t>USD 116651.00 - 161932.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28ea77a192b747e4a00fbc514f4ee22d-senior-staff-attorney-criminal-justice-and-police-practices-aclu-southern-california-los-angeles</t>
+  </si>
+  <si>
     <t>SFRRN Program Manager</t>
   </si>
   <si>
@@ -1744,6 +2326,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/2165f041705749c7a46542f6c1e50638-sfrrn-program-manager-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
   </si>
   <si>
+    <t>Site Director—Middle School Program</t>
+  </si>
+  <si>
+    <t>Breakthrough Houston</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a66eca395d864e10964de969cf655501-site-directormiddle-school-program-breakthrough-houston-houston</t>
+  </si>
+  <si>
+    <t>Small Animals Coordinator at Ambue Ari Sanctuary – Work with Rescued Wildlife in the Bolivian Rainforest</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>Ascensión de Guarayos, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>USD 200.00 - 200.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52fcfabf769d4596944ed5db86e8bf10-small-animals-coordinator-at-ambue-ari-sanctuary-work-with-rescued-wildlife-in-the-bolivian-rainforest-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
+    <t>Small Business Loan Officer</t>
+  </si>
+  <si>
+    <t>Northwest Access Fund</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ba2fb6390044d918babc4ea4283fd80-small-business-loan-officer-northwest-access-fund-seattle</t>
+  </si>
+  <si>
     <t>Social Worker, Adoptive Parent Services</t>
   </si>
   <si>
@@ -1762,15 +2389,24 @@
     <t>ssistant Attorney General: Real Property Bureau (3925)</t>
   </si>
   <si>
-    <t>New York State Office of the Attorney General</t>
-  </si>
-  <si>
-    <t>Albany, New York</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/government-job/bbe287b361764a869d0cd74a4715539a-ssistant-attorney-general-real-property-bureau-3925-new-york-state-office-of-the-attorney-general-albany</t>
   </si>
   <si>
+    <t>Staff Attorney - Housing &amp; Habitability</t>
+  </si>
+  <si>
+    <t>Legal Clinic for the Disabled</t>
+  </si>
+  <si>
+    <t>USD 67500.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ce850f0fdf24a38a6d7c2687dbe7747-staff-attorney-housing-habitability-legal-clinic-for-the-disabled-philadelphia</t>
+  </si>
+  <si>
     <t>Staff Attorney or Senior/Supervising Staff Attorney</t>
   </si>
   <si>
@@ -1789,21 +2425,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/93819134b41f4e2d9181b3c8386c7f80-staff-attorney-or-seniorsupervising-staff-attorney-rutgers-immigrant-rights-clinic-newark</t>
   </si>
   <si>
+    <t>Staff Attorney, Criminal Justice and Police Practices</t>
+  </si>
+  <si>
+    <t>USD 89068.00 - 106351.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54167b97e6d945bb9ec280c004a00139-staff-attorney-criminal-justice-and-police-practices-aclu-southern-california-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney, New York</t>
+  </si>
+  <si>
+    <t>The Young Center for Immigrant Children's Rights</t>
+  </si>
+  <si>
+    <t>USD 86882.45 - 99485.73/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7283b5f1ecef4729942bbec5eaaae97a-staff-attorney-new-york-the-young-center-for-immigrant-childrens-rights-new-york</t>
+  </si>
+  <si>
     <t>Staff Attorney, Phoenix</t>
   </si>
   <si>
-    <t>The Young Center for Immigrant Children's Rights</t>
-  </si>
-  <si>
     <t>Phoenix, Arizona</t>
   </si>
   <si>
     <t>USD 75550.80 - 86509.28/year</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/1d1da22aff1844fa8b27066cf1829d6f-staff-attorney-phoenix-the-young-center-for-immigrant-childrens-rights-phoenix</t>
   </si>
   <si>
@@ -1825,6 +2479,15 @@
     <t>https://www.idealist.org/en/job/3c2848a127534d4f8ef1b72041af6a5a-talent-operations-specialist-nyc-campaign-finance-board-new-york</t>
   </si>
   <si>
+    <t>Technology Support Specialist</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efa3e8eea0fe4a32b8335ffadada6e00-technology-support-specialist-girl-scout-council-of-the-nations-capital-washington</t>
+  </si>
+  <si>
     <t>Temporary Organizer</t>
   </si>
   <si>
@@ -1840,6 +2503,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/7ed9946e44f34b23b5d4d161683e9d88-temporary-organizer-safety-net-project-urban-justice-center-new-york</t>
   </si>
   <si>
+    <t>Tour Guide</t>
+  </si>
+  <si>
+    <t>Heurich House Museum</t>
+  </si>
+  <si>
+    <t>USD 20.50 - 20.50/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b8934c0afc84f54a328e53a7a36dca5-tour-guide-heurich-house-museum-washington</t>
+  </si>
+  <si>
+    <t>Training Manager</t>
+  </si>
+  <si>
+    <t>Fairfax Court Appointed Special Advocates (CASA)</t>
+  </si>
+  <si>
+    <t>Fairfax, VA</t>
+  </si>
+  <si>
+    <t>USD 32000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70ec793ce7a74b1aac3bd3344e183b53-training-manager-fairfax-court-appointed-special-advocates-casa-fairfax</t>
+  </si>
+  <si>
     <t>Trauma Therapist - 60% Full-Time - Counseling Center</t>
   </si>
   <si>
@@ -1876,6 +2569,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c59cad63d3d84bfab564d6f21495ae83-volunteer-manager-engagement-and-retention-the-good-dog-foundation-new-york</t>
   </si>
   <si>
+    <t>Volunteer Repack Coordinator</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>USD 27.50 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d603f3d5d6be4925b7630a900a62a2e6-volunteer-repack-coordinator-food-lifeline-seattle</t>
+  </si>
+  <si>
     <t>Watershed Intelligence Manager</t>
   </si>
   <si>
@@ -1907,6 +2615,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/6030db589ab645939e7e22a77fc1b525-writer-brand-and-editorial-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>Youth Engagement Assistant – AmeriCorps</t>
+  </si>
+  <si>
+    <t>SchoolTalk, Inc.</t>
+  </si>
+  <si>
+    <t>USD 25000.00 - 25000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd285efa16814a8f8cd84cc62564a910-youth-engagement-assistant-americorps-schooltalk-inc-washington</t>
   </si>
   <si>
     <t>Youth Workshop Facilitator</t>
@@ -3319,7 +4042,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3392,30 +4115,30 @@
         <v>230</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
         <v>238</v>
@@ -3438,266 +4161,266 @@
         <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
         <v>224</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="F6" t="s">
         <v>226</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
         <v>224</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D8" t="s">
         <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
         <v>224</v>
       </c>
       <c r="E9" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="F9" t="s">
         <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="D10" t="s">
         <v>224</v>
       </c>
       <c r="E10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F10" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s">
         <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="D12" t="s">
         <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F12" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C13" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D13" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
         <v>286</v>
       </c>
       <c r="F13" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" t="s">
         <v>289</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" t="s">
         <v>290</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D14" t="s">
-        <v>224</v>
-      </c>
-      <c r="E14" t="s">
-        <v>292</v>
-      </c>
-      <c r="F14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" t="s">
         <v>295</v>
       </c>
-      <c r="B15" t="s">
+      <c r="E15" t="s">
         <v>296</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>297</v>
       </c>
-      <c r="D15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H15" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="F15" t="s">
-        <v>299</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" t="s">
         <v>301</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" t="s">
         <v>302</v>
       </c>
-      <c r="C16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D16" t="s">
-        <v>224</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>303</v>
-      </c>
-      <c r="F16" t="s">
-        <v>226</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>304</v>
@@ -3705,1137 +4428,1137 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>299</v>
+      </c>
+      <c r="B17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" t="s">
         <v>305</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F17" t="s">
+        <v>303</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C17" t="s">
-        <v>223</v>
-      </c>
-      <c r="D17" t="s">
-        <v>224</v>
-      </c>
-      <c r="E17" t="s">
-        <v>307</v>
-      </c>
-      <c r="F17" t="s">
-        <v>308</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>312</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
         <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="F18" t="s">
-        <v>226</v>
+        <v>303</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="F19" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="D20" t="s">
         <v>224</v>
       </c>
       <c r="E20" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="F20" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="C21" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D21" t="s">
         <v>224</v>
       </c>
       <c r="E21" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="F21" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="B22" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="D22" t="s">
         <v>224</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>302</v>
       </c>
       <c r="F22" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="B23" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="D23" t="s">
         <v>224</v>
       </c>
       <c r="E23" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="F23" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B24" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="D24" t="s">
         <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="F24" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="C25" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D25" t="s">
         <v>224</v>
       </c>
       <c r="E25" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="F25" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B26" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="D26" t="s">
         <v>224</v>
       </c>
       <c r="E26" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="F26" t="s">
-        <v>226</v>
+        <v>335</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="B27" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>359</v>
+        <v>277</v>
       </c>
       <c r="D27" t="s">
         <v>224</v>
       </c>
       <c r="E27" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="F27" t="s">
-        <v>239</v>
+        <v>340</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="E28" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="F28" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="B29" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="D29" t="s">
         <v>224</v>
       </c>
       <c r="E29" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="F29" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C30" t="s">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="D30" t="s">
-        <v>376</v>
+        <v>224</v>
       </c>
       <c r="E30" t="s">
-        <v>226</v>
+        <v>356</v>
       </c>
       <c r="F30" t="s">
-        <v>226</v>
+        <v>357</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="B31" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C31" t="s">
-        <v>223</v>
+        <v>361</v>
       </c>
       <c r="D31" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="E31" t="s">
-        <v>238</v>
+        <v>363</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>364</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="B32" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C32" t="s">
-        <v>383</v>
+        <v>223</v>
       </c>
       <c r="D32" t="s">
         <v>224</v>
       </c>
       <c r="E32" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="F32" t="s">
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B33" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="C33" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E33" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="F33" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="D34" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E34" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="F34" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B35" t="s">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="C35" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E35" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="F35" t="s">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E36" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="F36" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="B37" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="C37" t="s">
         <v>223</v>
       </c>
       <c r="D37" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E37" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F37" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="C38" t="s">
-        <v>223</v>
+        <v>392</v>
       </c>
       <c r="D38" t="s">
-        <v>376</v>
+        <v>224</v>
       </c>
       <c r="E38" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="F38" t="s">
-        <v>416</v>
+        <v>226</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="C39" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E39" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="F39" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="C40" t="s">
-        <v>423</v>
+        <v>277</v>
       </c>
       <c r="D40" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E40" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="F40" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="C41" t="s">
-        <v>223</v>
+        <v>407</v>
       </c>
       <c r="D41" t="s">
-        <v>376</v>
+        <v>224</v>
       </c>
       <c r="E41" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="F41" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C42" t="s">
-        <v>434</v>
+        <v>277</v>
       </c>
       <c r="D42" t="s">
         <v>224</v>
       </c>
       <c r="E42" t="s">
-        <v>435</v>
+        <v>225</v>
       </c>
       <c r="F42" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="C43" t="s">
-        <v>236</v>
+        <v>417</v>
       </c>
       <c r="D43" t="s">
         <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="F43" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>444</v>
+        <v>293</v>
       </c>
       <c r="C44" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="D44" t="s">
         <v>224</v>
       </c>
       <c r="E44" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="F44" t="s">
-        <v>446</v>
+        <v>297</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="C45" t="s">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="D45" t="s">
         <v>224</v>
       </c>
       <c r="E45" t="s">
-        <v>254</v>
+        <v>427</v>
       </c>
       <c r="F45" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B46" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="C46" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="D46" t="s">
-        <v>376</v>
+        <v>224</v>
       </c>
       <c r="E46" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="F46" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="C47" t="s">
-        <v>459</v>
+        <v>371</v>
       </c>
       <c r="D47" t="s">
         <v>224</v>
       </c>
       <c r="E47" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="F47" t="s">
         <v>226</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="C48" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="D48" t="s">
         <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>464</v>
+        <v>296</v>
       </c>
       <c r="F48" t="s">
-        <v>465</v>
+        <v>246</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="C49" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="D49" t="s">
         <v>224</v>
       </c>
       <c r="E49" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F49" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="C50" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="D50" t="s">
         <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="F50" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="C51" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="D51" t="s">
         <v>224</v>
       </c>
       <c r="E51" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="F51" t="s">
-        <v>481</v>
+        <v>226</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="C52" t="s">
-        <v>223</v>
+        <v>462</v>
       </c>
       <c r="D52" t="s">
         <v>224</v>
       </c>
       <c r="E52" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="F52" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="C53" t="s">
-        <v>490</v>
+        <v>277</v>
       </c>
       <c r="D53" t="s">
         <v>224</v>
       </c>
       <c r="E53" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="F53" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s">
-        <v>495</v>
+        <v>317</v>
       </c>
       <c r="C54" t="s">
-        <v>496</v>
+        <v>318</v>
       </c>
       <c r="D54" t="s">
         <v>224</v>
       </c>
       <c r="E54" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="F54" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="C55" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="D55" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="E55" t="s">
-        <v>503</v>
+        <v>226</v>
       </c>
       <c r="F55" t="s">
-        <v>504</v>
+        <v>226</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s">
-        <v>242</v>
+        <v>480</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="D56" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E56" t="s">
-        <v>323</v>
+        <v>245</v>
       </c>
       <c r="F56" t="s">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C57" t="s">
-        <v>259</v>
+        <v>484</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="E57" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="F57" t="s">
-        <v>511</v>
+        <v>364</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="C58" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="D58" t="s">
         <v>224</v>
       </c>
       <c r="E58" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="F58" t="s">
-        <v>402</v>
+        <v>491</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="C59" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>224</v>
       </c>
       <c r="E59" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="F59" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>523</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="C60" t="s">
-        <v>297</v>
+        <v>499</v>
       </c>
       <c r="D60" t="s">
         <v>224</v>
       </c>
       <c r="E60" t="s">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="F60" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>528</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="C61" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="D61" t="s">
         <v>224</v>
       </c>
       <c r="E61" t="s">
-        <v>531</v>
+        <v>422</v>
       </c>
       <c r="F61" t="s">
-        <v>308</v>
+        <v>505</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s">
-        <v>379</v>
+        <v>508</v>
       </c>
       <c r="C62" t="s">
-        <v>223</v>
+        <v>509</v>
       </c>
       <c r="D62" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E62" t="s">
-        <v>238</v>
+        <v>510</v>
       </c>
       <c r="F62" t="s">
-        <v>280</v>
+        <v>511</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s">
-        <v>519</v>
+        <v>229</v>
       </c>
       <c r="C63" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
         <v>224</v>
       </c>
       <c r="E63" t="s">
-        <v>323</v>
+        <v>514</v>
       </c>
       <c r="F63" t="s">
-        <v>521</v>
+        <v>233</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="C64" t="s">
-        <v>539</v>
+        <v>277</v>
       </c>
       <c r="D64" t="s">
         <v>224</v>
       </c>
       <c r="E64" t="s">
-        <v>540</v>
+        <v>402</v>
       </c>
       <c r="F64" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="C65" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E65" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="F65" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="B66" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="C66" t="s">
         <v>223</v>
@@ -4844,427 +5567,1761 @@
         <v>224</v>
       </c>
       <c r="E66" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
       <c r="F66" t="s">
-        <v>350</v>
+        <v>226</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="B67" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="C67" t="s">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="D67" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E67" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="F67" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>556</v>
+        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="B68" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="C68" t="s">
-        <v>223</v>
+        <v>407</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E68" t="s">
-        <v>226</v>
+        <v>536</v>
       </c>
       <c r="F68" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="C69" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="D69" t="s">
         <v>224</v>
       </c>
       <c r="E69" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="F69" t="s">
-        <v>564</v>
+        <v>469</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="B70" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="C70" t="s">
-        <v>568</v>
+        <v>277</v>
       </c>
       <c r="D70" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E70" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="F70" t="s">
-        <v>280</v>
+        <v>546</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>570</v>
+        <v>547</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>571</v>
+        <v>548</v>
       </c>
       <c r="B71" t="s">
-        <v>572</v>
+        <v>549</v>
       </c>
       <c r="C71" t="s">
-        <v>479</v>
+        <v>223</v>
       </c>
       <c r="D71" t="s">
         <v>224</v>
       </c>
       <c r="E71" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="F71" t="s">
-        <v>574</v>
+        <v>551</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>576</v>
+        <v>118</v>
       </c>
       <c r="B72" t="s">
-        <v>577</v>
+        <v>553</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>554</v>
       </c>
       <c r="D72" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E72" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="F72" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="C73" t="s">
-        <v>583</v>
+        <v>223</v>
       </c>
       <c r="D73" t="s">
-        <v>224</v>
+        <v>362</v>
       </c>
       <c r="E73" t="s">
-        <v>226</v>
+        <v>560</v>
       </c>
       <c r="F73" t="s">
-        <v>226</v>
+        <v>561</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="B74" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="C74" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="D74" t="s">
         <v>224</v>
       </c>
       <c r="E74" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="F74" t="s">
-        <v>589</v>
+        <v>226</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="C75" t="s">
-        <v>593</v>
+        <v>312</v>
       </c>
       <c r="D75" t="s">
         <v>224</v>
       </c>
       <c r="E75" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="F75" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="B76" t="s">
-        <v>278</v>
+        <v>574</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>575</v>
       </c>
       <c r="D76" t="s">
         <v>224</v>
       </c>
       <c r="E76" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="F76" t="s">
-        <v>280</v>
+        <v>577</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>580</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D77" t="s">
         <v>224</v>
       </c>
       <c r="E77" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>582</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="B78" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>586</v>
       </c>
       <c r="D78" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="E78" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="F78" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="B79" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>592</v>
       </c>
       <c r="D79" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="E79" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F79" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s">
-        <v>614</v>
+        <v>535</v>
       </c>
       <c r="C80" t="s">
-        <v>223</v>
+        <v>407</v>
       </c>
       <c r="D80" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E80" t="s">
-        <v>615</v>
+        <v>536</v>
       </c>
       <c r="F80" t="s">
-        <v>385</v>
+        <v>594</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="B81" t="s">
-        <v>268</v>
+        <v>599</v>
       </c>
       <c r="C81" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="D81" t="s">
         <v>224</v>
       </c>
       <c r="E81" t="s">
-        <v>254</v>
+        <v>600</v>
       </c>
       <c r="F81" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="C82" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="D82" t="s">
         <v>224</v>
       </c>
       <c r="E82" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="F82" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="B83" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="C83" t="s">
-        <v>223</v>
+        <v>462</v>
       </c>
       <c r="D83" t="s">
         <v>224</v>
       </c>
       <c r="E83" t="s">
-        <v>628</v>
+        <v>272</v>
       </c>
       <c r="F83" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>613</v>
+      </c>
+      <c r="B84" t="s">
+        <v>333</v>
+      </c>
+      <c r="C84" t="s">
+        <v>614</v>
+      </c>
+      <c r="D84" t="s">
+        <v>224</v>
+      </c>
+      <c r="E84" t="s">
+        <v>334</v>
+      </c>
+      <c r="F84" t="s">
+        <v>335</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>616</v>
+      </c>
+      <c r="B85" t="s">
+        <v>617</v>
+      </c>
+      <c r="C85" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" t="s">
+        <v>362</v>
+      </c>
+      <c r="E85" t="s">
+        <v>618</v>
+      </c>
+      <c r="F85" t="s">
+        <v>619</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>621</v>
+      </c>
+      <c r="B86" t="s">
+        <v>622</v>
+      </c>
+      <c r="C86" t="s">
+        <v>623</v>
+      </c>
+      <c r="D86" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" t="s">
+        <v>624</v>
+      </c>
+      <c r="F86" t="s">
+        <v>335</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>621</v>
+      </c>
+      <c r="B87" t="s">
+        <v>626</v>
+      </c>
+      <c r="C87" t="s">
+        <v>627</v>
+      </c>
+      <c r="D87" t="s">
+        <v>224</v>
+      </c>
+      <c r="E87" t="s">
+        <v>628</v>
+      </c>
+      <c r="F87" t="s">
+        <v>629</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>631</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B88" t="s">
         <v>632</v>
       </c>
-      <c r="C84" t="s">
-        <v>273</v>
-      </c>
-      <c r="D84" t="s">
-        <v>376</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="C88" t="s">
         <v>633</v>
       </c>
-      <c r="F84" t="s">
+      <c r="D88" t="s">
+        <v>224</v>
+      </c>
+      <c r="E88" t="s">
         <v>634</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="F88" t="s">
+        <v>226</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>635</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>636</v>
+      </c>
+      <c r="B89" t="s">
+        <v>632</v>
+      </c>
+      <c r="C89" t="s">
+        <v>637</v>
+      </c>
+      <c r="D89" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" t="s">
+        <v>638</v>
+      </c>
+      <c r="F89" t="s">
+        <v>639</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>641</v>
+      </c>
+      <c r="B90" t="s">
+        <v>632</v>
+      </c>
+      <c r="C90" t="s">
+        <v>642</v>
+      </c>
+      <c r="D90" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s">
+        <v>634</v>
+      </c>
+      <c r="F90" t="s">
+        <v>643</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>645</v>
+      </c>
+      <c r="B91" t="s">
+        <v>569</v>
+      </c>
+      <c r="C91" t="s">
+        <v>314</v>
+      </c>
+      <c r="D91" t="s">
+        <v>224</v>
+      </c>
+      <c r="E91" t="s">
+        <v>570</v>
+      </c>
+      <c r="F91" t="s">
+        <v>646</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>648</v>
+      </c>
+      <c r="B92" t="s">
+        <v>649</v>
+      </c>
+      <c r="C92" t="s">
+        <v>650</v>
+      </c>
+      <c r="D92" t="s">
+        <v>224</v>
+      </c>
+      <c r="E92" t="s">
+        <v>651</v>
+      </c>
+      <c r="F92" t="s">
+        <v>652</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>654</v>
+      </c>
+      <c r="B93" t="s">
+        <v>622</v>
+      </c>
+      <c r="C93" t="s">
+        <v>314</v>
+      </c>
+      <c r="D93" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" t="s">
+        <v>655</v>
+      </c>
+      <c r="F93" t="s">
+        <v>335</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>657</v>
+      </c>
+      <c r="B94" t="s">
+        <v>658</v>
+      </c>
+      <c r="C94" t="s">
+        <v>659</v>
+      </c>
+      <c r="D94" t="s">
+        <v>224</v>
+      </c>
+      <c r="E94" t="s">
+        <v>660</v>
+      </c>
+      <c r="F94" t="s">
+        <v>607</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>662</v>
+      </c>
+      <c r="B95" t="s">
+        <v>663</v>
+      </c>
+      <c r="C95" t="s">
+        <v>223</v>
+      </c>
+      <c r="D95" t="s">
+        <v>224</v>
+      </c>
+      <c r="E95" t="s">
+        <v>664</v>
+      </c>
+      <c r="F95" t="s">
+        <v>665</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>667</v>
+      </c>
+      <c r="B96" t="s">
+        <v>668</v>
+      </c>
+      <c r="C96" t="s">
+        <v>426</v>
+      </c>
+      <c r="D96" t="s">
+        <v>224</v>
+      </c>
+      <c r="E96" t="s">
+        <v>669</v>
+      </c>
+      <c r="F96" t="s">
+        <v>670</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>672</v>
+      </c>
+      <c r="B97" t="s">
+        <v>673</v>
+      </c>
+      <c r="C97" t="s">
+        <v>674</v>
+      </c>
+      <c r="D97" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" t="s">
+        <v>675</v>
+      </c>
+      <c r="F97" t="s">
+        <v>676</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>678</v>
+      </c>
+      <c r="B98" t="s">
+        <v>679</v>
+      </c>
+      <c r="C98" t="s">
+        <v>680</v>
+      </c>
+      <c r="D98" t="s">
+        <v>244</v>
+      </c>
+      <c r="E98" t="s">
+        <v>681</v>
+      </c>
+      <c r="F98" t="s">
+        <v>682</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>684</v>
+      </c>
+      <c r="B99" t="s">
+        <v>254</v>
+      </c>
+      <c r="C99" t="s">
+        <v>255</v>
+      </c>
+      <c r="D99" t="s">
+        <v>224</v>
+      </c>
+      <c r="E99" t="s">
+        <v>402</v>
+      </c>
+      <c r="F99" t="s">
+        <v>257</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>686</v>
+      </c>
+      <c r="B100" t="s">
+        <v>687</v>
+      </c>
+      <c r="C100" t="s">
+        <v>277</v>
+      </c>
+      <c r="D100" t="s">
+        <v>224</v>
+      </c>
+      <c r="E100" t="s">
+        <v>688</v>
+      </c>
+      <c r="F100" t="s">
+        <v>689</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>691</v>
+      </c>
+      <c r="B101" t="s">
+        <v>692</v>
+      </c>
+      <c r="C101" t="s">
+        <v>693</v>
+      </c>
+      <c r="D101" t="s">
+        <v>224</v>
+      </c>
+      <c r="E101" t="s">
+        <v>694</v>
+      </c>
+      <c r="F101" t="s">
+        <v>511</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>691</v>
+      </c>
+      <c r="B102" t="s">
+        <v>696</v>
+      </c>
+      <c r="C102" t="s">
+        <v>697</v>
+      </c>
+      <c r="D102" t="s">
+        <v>224</v>
+      </c>
+      <c r="E102" t="s">
+        <v>698</v>
+      </c>
+      <c r="F102" t="s">
+        <v>699</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>701</v>
+      </c>
+      <c r="B103" t="s">
+        <v>702</v>
+      </c>
+      <c r="C103" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103" t="s">
+        <v>224</v>
+      </c>
+      <c r="E103" t="s">
+        <v>703</v>
+      </c>
+      <c r="F103" t="s">
+        <v>704</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>706</v>
+      </c>
+      <c r="B104" t="s">
+        <v>707</v>
+      </c>
+      <c r="C104" t="s">
+        <v>310</v>
+      </c>
+      <c r="D104" t="s">
+        <v>224</v>
+      </c>
+      <c r="E104" t="s">
+        <v>708</v>
+      </c>
+      <c r="F104" t="s">
+        <v>709</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>711</v>
+      </c>
+      <c r="B105" t="s">
+        <v>712</v>
+      </c>
+      <c r="C105" t="s">
+        <v>713</v>
+      </c>
+      <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" t="s">
+        <v>714</v>
+      </c>
+      <c r="F105" t="s">
+        <v>388</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>716</v>
+      </c>
+      <c r="B106" t="s">
+        <v>480</v>
+      </c>
+      <c r="C106" t="s">
+        <v>223</v>
+      </c>
+      <c r="D106" t="s">
+        <v>231</v>
+      </c>
+      <c r="E106" t="s">
+        <v>245</v>
+      </c>
+      <c r="F106" t="s">
+        <v>340</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>718</v>
+      </c>
+      <c r="B107" t="s">
+        <v>702</v>
+      </c>
+      <c r="C107" t="s">
+        <v>312</v>
+      </c>
+      <c r="D107" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" t="s">
+        <v>402</v>
+      </c>
+      <c r="F107" t="s">
+        <v>704</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>720</v>
+      </c>
+      <c r="B108" t="s">
+        <v>564</v>
+      </c>
+      <c r="C108" t="s">
+        <v>350</v>
+      </c>
+      <c r="D108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E108" t="s">
+        <v>721</v>
+      </c>
+      <c r="F108" t="s">
+        <v>226</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>723</v>
+      </c>
+      <c r="B109" t="s">
+        <v>724</v>
+      </c>
+      <c r="C109" t="s">
+        <v>725</v>
+      </c>
+      <c r="D109" t="s">
+        <v>224</v>
+      </c>
+      <c r="E109" t="s">
+        <v>726</v>
+      </c>
+      <c r="F109" t="s">
+        <v>727</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>729</v>
+      </c>
+      <c r="B110" t="s">
+        <v>730</v>
+      </c>
+      <c r="C110" t="s">
+        <v>312</v>
+      </c>
+      <c r="D110" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" t="s">
+        <v>731</v>
+      </c>
+      <c r="F110" t="s">
+        <v>732</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>734</v>
+      </c>
+      <c r="B111" t="s">
+        <v>735</v>
+      </c>
+      <c r="C111" t="s">
+        <v>223</v>
+      </c>
+      <c r="D111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" t="s">
+        <v>736</v>
+      </c>
+      <c r="F111" t="s">
+        <v>433</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>738</v>
+      </c>
+      <c r="B112" t="s">
+        <v>739</v>
+      </c>
+      <c r="C112" t="s">
+        <v>223</v>
+      </c>
+      <c r="D112" t="s">
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
+        <v>740</v>
+      </c>
+      <c r="F112" t="s">
+        <v>741</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>743</v>
+      </c>
+      <c r="B113" t="s">
+        <v>744</v>
+      </c>
+      <c r="C113" t="s">
+        <v>310</v>
+      </c>
+      <c r="D113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E113" t="s">
+        <v>655</v>
+      </c>
+      <c r="F113" t="s">
+        <v>745</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>747</v>
+      </c>
+      <c r="B114" t="s">
+        <v>748</v>
+      </c>
+      <c r="C114" t="s">
+        <v>223</v>
+      </c>
+      <c r="D114" t="s">
+        <v>224</v>
+      </c>
+      <c r="E114" t="s">
+        <v>226</v>
+      </c>
+      <c r="F114" t="s">
+        <v>749</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>751</v>
+      </c>
+      <c r="B115" t="s">
+        <v>752</v>
+      </c>
+      <c r="C115" t="s">
+        <v>441</v>
+      </c>
+      <c r="D115" t="s">
+        <v>224</v>
+      </c>
+      <c r="E115" t="s">
+        <v>698</v>
+      </c>
+      <c r="F115" t="s">
+        <v>753</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>755</v>
+      </c>
+      <c r="B116" t="s">
+        <v>756</v>
+      </c>
+      <c r="C116" t="s">
+        <v>757</v>
+      </c>
+      <c r="D116" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" t="s">
+        <v>758</v>
+      </c>
+      <c r="F116" t="s">
+        <v>340</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>760</v>
+      </c>
+      <c r="B117" t="s">
+        <v>761</v>
+      </c>
+      <c r="C117" t="s">
+        <v>445</v>
+      </c>
+      <c r="D117" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
+        <v>762</v>
+      </c>
+      <c r="F117" t="s">
+        <v>763</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>765</v>
+      </c>
+      <c r="B118" t="s">
+        <v>766</v>
+      </c>
+      <c r="C118" t="s">
+        <v>659</v>
+      </c>
+      <c r="D118" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" t="s">
+        <v>767</v>
+      </c>
+      <c r="F118" t="s">
+        <v>768</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>770</v>
+      </c>
+      <c r="B119" t="s">
+        <v>771</v>
+      </c>
+      <c r="C119" t="s">
+        <v>772</v>
+      </c>
+      <c r="D119" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" t="s">
+        <v>587</v>
+      </c>
+      <c r="F119" t="s">
+        <v>773</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>775</v>
+      </c>
+      <c r="B120" t="s">
+        <v>776</v>
+      </c>
+      <c r="C120" t="s">
+        <v>777</v>
+      </c>
+      <c r="D120" t="s">
+        <v>224</v>
+      </c>
+      <c r="E120" t="s">
+        <v>778</v>
+      </c>
+      <c r="F120" t="s">
+        <v>779</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>781</v>
+      </c>
+      <c r="B121" t="s">
+        <v>782</v>
+      </c>
+      <c r="C121" t="s">
+        <v>223</v>
+      </c>
+      <c r="D121" t="s">
+        <v>224</v>
+      </c>
+      <c r="E121" t="s">
+        <v>675</v>
+      </c>
+      <c r="F121" t="s">
+        <v>783</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>785</v>
+      </c>
+      <c r="B122" t="s">
+        <v>786</v>
+      </c>
+      <c r="C122" t="s">
+        <v>277</v>
+      </c>
+      <c r="D122" t="s">
+        <v>224</v>
+      </c>
+      <c r="E122" t="s">
+        <v>787</v>
+      </c>
+      <c r="F122" t="s">
+        <v>788</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>790</v>
+      </c>
+      <c r="B123" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" t="s">
+        <v>250</v>
+      </c>
+      <c r="D123" t="s">
+        <v>224</v>
+      </c>
+      <c r="E123" t="s">
+        <v>226</v>
+      </c>
+      <c r="F123" t="s">
+        <v>226</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>792</v>
+      </c>
+      <c r="B124" t="s">
+        <v>793</v>
+      </c>
+      <c r="C124" t="s">
+        <v>371</v>
+      </c>
+      <c r="D124" t="s">
+        <v>224</v>
+      </c>
+      <c r="E124" t="s">
+        <v>794</v>
+      </c>
+      <c r="F124" t="s">
+        <v>795</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>797</v>
+      </c>
+      <c r="B125" t="s">
+        <v>798</v>
+      </c>
+      <c r="C125" t="s">
+        <v>799</v>
+      </c>
+      <c r="D125" t="s">
+        <v>224</v>
+      </c>
+      <c r="E125" t="s">
+        <v>800</v>
+      </c>
+      <c r="F125" t="s">
+        <v>801</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>803</v>
+      </c>
+      <c r="B126" t="s">
+        <v>761</v>
+      </c>
+      <c r="C126" t="s">
+        <v>445</v>
+      </c>
+      <c r="D126" t="s">
+        <v>224</v>
+      </c>
+      <c r="E126" t="s">
+        <v>804</v>
+      </c>
+      <c r="F126" t="s">
+        <v>763</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>806</v>
+      </c>
+      <c r="B127" t="s">
+        <v>807</v>
+      </c>
+      <c r="C127" t="s">
+        <v>277</v>
+      </c>
+      <c r="D127" t="s">
+        <v>224</v>
+      </c>
+      <c r="E127" t="s">
+        <v>808</v>
+      </c>
+      <c r="F127" t="s">
+        <v>809</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>811</v>
+      </c>
+      <c r="B128" t="s">
+        <v>807</v>
+      </c>
+      <c r="C128" t="s">
+        <v>812</v>
+      </c>
+      <c r="D128" t="s">
+        <v>224</v>
+      </c>
+      <c r="E128" t="s">
+        <v>813</v>
+      </c>
+      <c r="F128" t="s">
+        <v>809</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>815</v>
+      </c>
+      <c r="B129" t="s">
+        <v>338</v>
+      </c>
+      <c r="C129" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129" t="s">
+        <v>224</v>
+      </c>
+      <c r="E129" t="s">
+        <v>816</v>
+      </c>
+      <c r="F129" t="s">
+        <v>340</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>818</v>
+      </c>
+      <c r="B130" t="s">
+        <v>285</v>
+      </c>
+      <c r="C130" t="s">
+        <v>277</v>
+      </c>
+      <c r="D130" t="s">
+        <v>224</v>
+      </c>
+      <c r="E130" t="s">
+        <v>819</v>
+      </c>
+      <c r="F130" t="s">
+        <v>226</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>821</v>
+      </c>
+      <c r="B131" t="s">
+        <v>604</v>
+      </c>
+      <c r="C131" t="s">
+        <v>312</v>
+      </c>
+      <c r="D131" t="s">
+        <v>224</v>
+      </c>
+      <c r="E131" t="s">
+        <v>822</v>
+      </c>
+      <c r="F131" t="s">
+        <v>607</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>824</v>
+      </c>
+      <c r="B132" t="s">
+        <v>825</v>
+      </c>
+      <c r="C132" t="s">
+        <v>277</v>
+      </c>
+      <c r="D132" t="s">
+        <v>295</v>
+      </c>
+      <c r="E132" t="s">
+        <v>826</v>
+      </c>
+      <c r="F132" t="s">
+        <v>827</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>829</v>
+      </c>
+      <c r="B133" t="s">
+        <v>830</v>
+      </c>
+      <c r="C133" t="s">
+        <v>312</v>
+      </c>
+      <c r="D133" t="s">
+        <v>231</v>
+      </c>
+      <c r="E133" t="s">
+        <v>831</v>
+      </c>
+      <c r="F133" t="s">
+        <v>832</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>834</v>
+      </c>
+      <c r="B134" t="s">
+        <v>835</v>
+      </c>
+      <c r="C134" t="s">
+        <v>836</v>
+      </c>
+      <c r="D134" t="s">
+        <v>231</v>
+      </c>
+      <c r="E134" t="s">
+        <v>837</v>
+      </c>
+      <c r="F134" t="s">
+        <v>652</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>839</v>
+      </c>
+      <c r="B135" t="s">
+        <v>840</v>
+      </c>
+      <c r="C135" t="s">
+        <v>277</v>
+      </c>
+      <c r="D135" t="s">
+        <v>231</v>
+      </c>
+      <c r="E135" t="s">
+        <v>841</v>
+      </c>
+      <c r="F135" t="s">
+        <v>842</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>844</v>
+      </c>
+      <c r="B136" t="s">
+        <v>845</v>
+      </c>
+      <c r="C136" t="s">
+        <v>223</v>
+      </c>
+      <c r="D136" t="s">
+        <v>224</v>
+      </c>
+      <c r="E136" t="s">
+        <v>846</v>
+      </c>
+      <c r="F136" t="s">
+        <v>491</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>848</v>
+      </c>
+      <c r="B137" t="s">
+        <v>289</v>
+      </c>
+      <c r="C137" t="s">
+        <v>223</v>
+      </c>
+      <c r="D137" t="s">
+        <v>224</v>
+      </c>
+      <c r="E137" t="s">
+        <v>272</v>
+      </c>
+      <c r="F137" t="s">
+        <v>849</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>851</v>
+      </c>
+      <c r="B138" t="s">
+        <v>852</v>
+      </c>
+      <c r="C138" t="s">
+        <v>407</v>
+      </c>
+      <c r="D138" t="s">
+        <v>224</v>
+      </c>
+      <c r="E138" t="s">
+        <v>853</v>
+      </c>
+      <c r="F138" t="s">
+        <v>854</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>856</v>
+      </c>
+      <c r="B139" t="s">
+        <v>857</v>
+      </c>
+      <c r="C139" t="s">
+        <v>858</v>
+      </c>
+      <c r="D139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E139" t="s">
+        <v>859</v>
+      </c>
+      <c r="F139" t="s">
+        <v>860</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>862</v>
+      </c>
+      <c r="B140" t="s">
+        <v>863</v>
+      </c>
+      <c r="C140" t="s">
+        <v>223</v>
+      </c>
+      <c r="D140" t="s">
+        <v>224</v>
+      </c>
+      <c r="E140" t="s">
+        <v>864</v>
+      </c>
+      <c r="F140" t="s">
+        <v>865</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>867</v>
+      </c>
+      <c r="B141" t="s">
+        <v>868</v>
+      </c>
+      <c r="C141" t="s">
+        <v>312</v>
+      </c>
+      <c r="D141" t="s">
+        <v>295</v>
+      </c>
+      <c r="E141" t="s">
+        <v>869</v>
+      </c>
+      <c r="F141" t="s">
+        <v>870</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>872</v>
+      </c>
+      <c r="B142" t="s">
+        <v>873</v>
+      </c>
+      <c r="C142" t="s">
+        <v>312</v>
+      </c>
+      <c r="D142" t="s">
+        <v>362</v>
+      </c>
+      <c r="E142" t="s">
+        <v>874</v>
+      </c>
+      <c r="F142" t="s">
+        <v>875</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -5353,6 +7410,64 @@
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
     <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
